--- a/amir_adv/results/temp/ecxel_1.xlsx
+++ b/amir_adv/results/temp/ecxel_1.xlsx
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -275,24 +275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -703,18 +685,18 @@
     </row>
     <row r="2" ht="18" customFormat="1" customHeight="1" s="25">
       <c r="A2" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B2" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C2" s="36" t="inlineStr">
         <is>
-          <t>17/1</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="D2" s="36" t="n">
-        <v>132.45</v>
+        <v>104.13</v>
       </c>
       <c r="E2" s="21" t="n"/>
       <c r="F2" s="21" t="n"/>
@@ -723,13 +705,11 @@
       <c r="I2" s="21" t="n"/>
       <c r="J2" s="37" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>לוי עומר</t>
         </is>
       </c>
-      <c r="K2" s="37" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
+      <c r="K2" s="37" t="n">
+        <v>211967955</v>
       </c>
       <c r="L2" s="36" t="inlineStr">
         <is>
@@ -753,18 +733,18 @@
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B3" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>17/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="D3" s="36" t="n">
-        <v>138.45</v>
+        <v>105.03</v>
       </c>
       <c r="E3" s="13" t="n"/>
       <c r="F3" s="13" t="n"/>
@@ -773,30 +753,20 @@
       <c r="I3" s="13" t="n"/>
       <c r="J3" s="39" t="inlineStr">
         <is>
-          <t>בלולו חגית</t>
+          <t>טורגמן רויטל ירדנה</t>
         </is>
       </c>
       <c r="K3" s="39" t="n">
-        <v>34448431</v>
+        <v>25419128</v>
       </c>
       <c r="L3" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M3" s="38" t="inlineStr">
-        <is>
-          <t>בלולו טירן</t>
-        </is>
-      </c>
-      <c r="N3" s="38" t="n">
-        <v>22679740</v>
-      </c>
-      <c r="O3" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="M3" s="38" t="inlineStr"/>
+      <c r="N3" s="38" t="inlineStr"/>
+      <c r="O3" s="13" t="n"/>
       <c r="P3" s="16" t="n"/>
       <c r="Q3" s="13" t="n"/>
       <c r="R3" s="13" t="n"/>
@@ -811,18 +781,18 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B4" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>17/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="D4" s="36" t="n">
-        <v>153.1</v>
+        <v>104.49</v>
       </c>
       <c r="E4" s="13" t="n"/>
       <c r="F4" s="13" t="n"/>
@@ -831,24 +801,26 @@
       <c r="I4" s="13" t="n"/>
       <c r="J4" s="39" t="inlineStr">
         <is>
-          <t>פיטוסי דוד יוסף</t>
+          <t>כהן יהושע</t>
         </is>
       </c>
       <c r="K4" s="39" t="n">
-        <v>24929051</v>
+        <v>52037934</v>
       </c>
       <c r="L4" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr"/>
-      <c r="N4" s="36" t="inlineStr"/>
-      <c r="O4" s="36" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>יאסיוק אולגה</t>
         </is>
       </c>
+      <c r="N4" s="36" t="n">
+        <v>319422473</v>
+      </c>
+      <c r="O4" s="13" t="n"/>
       <c r="P4" s="16" t="n"/>
       <c r="Q4" s="13" t="n"/>
       <c r="R4" s="13" t="n"/>
@@ -863,18 +835,18 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B5" s="40" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>17/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="D5" s="40" t="n">
-        <v>134.8</v>
+        <v>105.36</v>
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="17" t="n"/>
@@ -883,13 +855,11 @@
       <c r="I5" s="17" t="n"/>
       <c r="J5" s="39" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>הרצן קורל</t>
         </is>
       </c>
-      <c r="K5" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
+      <c r="K5" s="39" t="n">
+        <v>316265677</v>
       </c>
       <c r="L5" s="40" t="inlineStr">
         <is>
@@ -913,18 +883,18 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B6" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>17/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="D6" s="36" t="n">
-        <v>149.25</v>
+        <v>104.49</v>
       </c>
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="13" t="n"/>
@@ -933,22 +903,30 @@
       <c r="I6" s="13" t="n"/>
       <c r="J6" s="39" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>זפרני אור</t>
         </is>
       </c>
-      <c r="K6" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
+      <c r="K6" s="39" t="n">
+        <v>305355877</v>
       </c>
       <c r="L6" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M6" s="36" t="inlineStr"/>
-      <c r="N6" s="36" t="inlineStr"/>
-      <c r="O6" s="13" t="n"/>
+      <c r="M6" s="36" t="inlineStr">
+        <is>
+          <t>זפרני עדן עדנה</t>
+        </is>
+      </c>
+      <c r="N6" s="36" t="n">
+        <v>208891622</v>
+      </c>
+      <c r="O6" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P6" s="16" t="n"/>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
@@ -963,18 +941,18 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B7" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>17/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>155.8</v>
+        <v>105.36</v>
       </c>
       <c r="E7" s="13" t="n"/>
       <c r="F7" s="13" t="n"/>
@@ -983,22 +961,30 @@
       <c r="I7" s="13" t="n"/>
       <c r="J7" s="37" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>חבורוסטיאנוב מקסים</t>
         </is>
       </c>
-      <c r="K7" s="37" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
+      <c r="K7" s="37" t="n">
+        <v>324309129</v>
       </c>
       <c r="L7" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr"/>
-      <c r="N7" s="36" t="inlineStr"/>
-      <c r="O7" s="13" t="n"/>
+      <c r="M7" s="36" t="inlineStr">
+        <is>
+          <t>סרגייב ויקטוריה</t>
+        </is>
+      </c>
+      <c r="N7" s="36" t="n">
+        <v>342571924</v>
+      </c>
+      <c r="O7" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P7" s="16" t="n"/>
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="13" t="n"/>
@@ -1013,18 +999,18 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B8" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>17/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="D8" s="36" t="n">
-        <v>119.15</v>
+        <v>104.49</v>
       </c>
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="21" t="n"/>
@@ -1033,20 +1019,30 @@
       <c r="I8" s="13" t="n"/>
       <c r="J8" s="39" t="inlineStr">
         <is>
-          <t>שרביט צחי</t>
+          <t>גורובוי אלכסנדר</t>
         </is>
       </c>
       <c r="K8" s="39" t="n">
-        <v>36177038</v>
+        <v>310230008</v>
       </c>
       <c r="L8" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M8" s="36" t="inlineStr"/>
-      <c r="N8" s="36" t="inlineStr"/>
-      <c r="O8" s="13" t="n"/>
+      <c r="M8" s="36" t="inlineStr">
+        <is>
+          <t>גורובוי ולנטינה</t>
+        </is>
+      </c>
+      <c r="N8" s="36" t="n">
+        <v>319273918</v>
+      </c>
+      <c r="O8" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P8" s="16" t="n"/>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
@@ -1061,18 +1057,20 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B9" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>17/8</t>
+          <t>2/8</t>
         </is>
       </c>
-      <c r="D9" s="36" t="n">
-        <v>141.75</v>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
       </c>
       <c r="E9" s="13" t="n"/>
       <c r="F9" s="13" t="n"/>
@@ -1081,15 +1079,15 @@
       <c r="I9" s="13" t="n"/>
       <c r="J9" s="39" t="inlineStr">
         <is>
-          <t>ביטון אלעד</t>
+          <t>דדון נטלי אני</t>
         </is>
       </c>
       <c r="K9" s="37" t="n">
-        <v>39804430</v>
+        <v>300129293</v>
       </c>
       <c r="L9" s="36" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="M9" s="36" t="inlineStr"/>
@@ -1109,18 +1107,18 @@
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B10" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>17/9</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>90.95</v>
+        <v>150.33</v>
       </c>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
@@ -1129,19 +1127,25 @@
       <c r="I10" s="13" t="n"/>
       <c r="J10" s="39" t="inlineStr">
         <is>
-          <t>בלנדר רוני מלכה</t>
+          <t>רודינסקי אלכסנדר</t>
         </is>
       </c>
       <c r="K10" s="39" t="n">
-        <v>302284252</v>
+        <v>307044941</v>
       </c>
       <c r="L10" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M10" s="36" t="inlineStr"/>
-      <c r="N10" s="36" t="inlineStr"/>
+      <c r="M10" s="36" t="inlineStr">
+        <is>
+          <t>רודינסקי יוליה</t>
+        </is>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>310229976</v>
+      </c>
       <c r="O10" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -1161,18 +1165,18 @@
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B11" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>17/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="D11" s="36" t="n">
-        <v>146.65</v>
+        <v>109.82</v>
       </c>
       <c r="E11" s="13" t="n"/>
       <c r="F11" s="13" t="n"/>
@@ -1181,20 +1185,30 @@
       <c r="I11" s="13" t="n"/>
       <c r="J11" s="39" t="inlineStr">
         <is>
-          <t>אראבוב חנה</t>
+          <t>שוקרון אשר פורטונטו</t>
         </is>
       </c>
       <c r="K11" s="39" t="n">
-        <v>305263444</v>
+        <v>65359481</v>
       </c>
       <c r="L11" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M11" s="36" t="inlineStr"/>
-      <c r="N11" s="36" t="inlineStr"/>
-      <c r="O11" s="13" t="n"/>
+      <c r="M11" s="36" t="inlineStr">
+        <is>
+          <t>שוקרון קוטי</t>
+        </is>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>67584425</v>
+      </c>
+      <c r="O11" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P11" s="16" t="n"/>
       <c r="Q11" s="13" t="n"/>
       <c r="R11" s="13" t="n"/>
@@ -1209,18 +1223,18 @@
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B12" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>17/11</t>
+          <t>2/11</t>
         </is>
       </c>
       <c r="D12" s="36" t="n">
-        <v>128.15</v>
+        <v>111.68</v>
       </c>
       <c r="E12" s="13" t="n"/>
       <c r="F12" s="13" t="n"/>
@@ -1229,11 +1243,11 @@
       <c r="I12" s="13" t="n"/>
       <c r="J12" s="39" t="inlineStr">
         <is>
-          <t>אהרן יהודה</t>
+          <t>דניאלי יורם</t>
         </is>
       </c>
       <c r="K12" s="39" t="n">
-        <v>305030173</v>
+        <v>57134223</v>
       </c>
       <c r="L12" s="36" t="inlineStr">
         <is>
@@ -1257,18 +1271,18 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B13" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>17/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="D13" s="36" t="n">
-        <v>119.15</v>
+        <v>111.44</v>
       </c>
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="13" t="n"/>
@@ -1277,11 +1291,11 @@
       <c r="I13" s="13" t="n"/>
       <c r="J13" s="39" t="inlineStr">
         <is>
-          <t>משיח תמרה</t>
+          <t>מרגוליס מרק</t>
         </is>
       </c>
       <c r="K13" s="39" t="n">
-        <v>17238502</v>
+        <v>311715817</v>
       </c>
       <c r="L13" s="36" t="inlineStr">
         <is>
@@ -1305,18 +1319,18 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B14" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>17/13</t>
+          <t>2/13</t>
         </is>
       </c>
       <c r="D14" s="36" t="n">
-        <v>141.75</v>
+        <v>127.14</v>
       </c>
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
@@ -1325,24 +1339,20 @@
       <c r="I14" s="13" t="n"/>
       <c r="J14" s="39" t="inlineStr">
         <is>
-          <t>טמארוב הילה</t>
+          <t>רוזמבלט מאיר</t>
         </is>
       </c>
       <c r="K14" s="39" t="n">
-        <v>301747887</v>
+        <v>322158858</v>
       </c>
       <c r="L14" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="M14" s="36" t="inlineStr"/>
       <c r="N14" s="36" t="inlineStr"/>
-      <c r="O14" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="O14" s="13" t="n"/>
       <c r="P14" s="16" t="n"/>
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
@@ -1357,18 +1367,18 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B15" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>17/14</t>
+          <t>2/14</t>
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>90.95</v>
+        <v>111.44</v>
       </c>
       <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
@@ -1377,11 +1387,11 @@
       <c r="I15" s="13" t="n"/>
       <c r="J15" s="39" t="inlineStr">
         <is>
-          <t>מסמי גאולה</t>
+          <t>זפרני שירן</t>
         </is>
       </c>
       <c r="K15" s="39" t="n">
-        <v>54733571</v>
+        <v>46231866</v>
       </c>
       <c r="L15" s="36" t="inlineStr">
         <is>
@@ -1405,18 +1415,18 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B16" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>17/15</t>
+          <t>2/15</t>
         </is>
       </c>
       <c r="D16" s="36" t="n">
-        <v>146.65</v>
+        <v>127.14</v>
       </c>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
@@ -1425,11 +1435,11 @@
       <c r="I16" s="13" t="n"/>
       <c r="J16" s="39" t="inlineStr">
         <is>
-          <t>שמש חפציבה</t>
+          <t>עמית דקל</t>
         </is>
       </c>
       <c r="K16" s="39" t="n">
-        <v>201134442</v>
+        <v>34204818</v>
       </c>
       <c r="L16" s="36" t="inlineStr">
         <is>
@@ -1438,11 +1448,11 @@
       </c>
       <c r="M16" s="36" t="inlineStr">
         <is>
-          <t>שמש יעקב</t>
+          <t>עמית ורד</t>
         </is>
       </c>
       <c r="N16" s="36" t="n">
-        <v>300489903</v>
+        <v>31507882</v>
       </c>
       <c r="O16" s="36" t="inlineStr">
         <is>
@@ -1463,18 +1473,18 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B17" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>17/16</t>
+          <t>2/16</t>
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>128.15</v>
+        <v>111.44</v>
       </c>
       <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
@@ -1483,20 +1493,30 @@
       <c r="I17" s="13" t="n"/>
       <c r="J17" s="39" t="inlineStr">
         <is>
-          <t>יסמין מיכל</t>
+          <t>גידקר אלעד</t>
         </is>
       </c>
       <c r="K17" s="39" t="n">
-        <v>32173080</v>
+        <v>300052677</v>
       </c>
       <c r="L17" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M17" s="36" t="inlineStr"/>
-      <c r="N17" s="36" t="inlineStr"/>
-      <c r="O17" s="13" t="n"/>
+      <c r="M17" s="36" t="inlineStr">
+        <is>
+          <t>גאן גידקר נוי קייט</t>
+        </is>
+      </c>
+      <c r="N17" s="36" t="n">
+        <v>203157706</v>
+      </c>
+      <c r="O17" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P17" s="16" t="n"/>
       <c r="Q17" s="13" t="n"/>
       <c r="R17" s="13" t="n"/>
@@ -1511,18 +1531,18 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B18" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>2/17</t>
         </is>
       </c>
       <c r="D18" s="36" t="n">
-        <v>119.15</v>
+        <v>127.14</v>
       </c>
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="n"/>
@@ -1531,11 +1551,11 @@
       <c r="I18" s="13" t="n"/>
       <c r="J18" s="39" t="inlineStr">
         <is>
-          <t>מתתיהו ברכה קרין</t>
+          <t>כהן אבישי</t>
         </is>
       </c>
       <c r="K18" s="39" t="n">
-        <v>207376542</v>
+        <v>303020804</v>
       </c>
       <c r="L18" s="36" t="inlineStr">
         <is>
@@ -1559,18 +1579,18 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B19" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>2/18</t>
         </is>
       </c>
       <c r="D19" s="36" t="n">
-        <v>141.75</v>
+        <v>111.44</v>
       </c>
       <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="n"/>
@@ -1579,19 +1599,25 @@
       <c r="I19" s="13" t="n"/>
       <c r="J19" s="39" t="inlineStr">
         <is>
-          <t>ימין מור</t>
+          <t>רוזמבלט רוסלן</t>
         </is>
       </c>
       <c r="K19" s="39" t="n">
-        <v>21938238</v>
+        <v>318027257</v>
       </c>
       <c r="L19" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M19" s="36" t="inlineStr"/>
-      <c r="N19" s="36" t="inlineStr"/>
+      <c r="M19" s="36" t="inlineStr">
+        <is>
+          <t>רוזמבלט ויקטוריה</t>
+        </is>
+      </c>
+      <c r="N19" s="36" t="n">
+        <v>321362212</v>
+      </c>
       <c r="O19" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -1611,18 +1637,18 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B20" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C20" s="36" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>2/19</t>
         </is>
       </c>
       <c r="D20" s="36" t="n">
-        <v>90.95</v>
+        <v>127.14</v>
       </c>
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="n"/>
@@ -1631,11 +1657,11 @@
       <c r="I20" s="13" t="n"/>
       <c r="J20" s="39" t="inlineStr">
         <is>
-          <t>כהן רות</t>
+          <t>לוזון רון</t>
         </is>
       </c>
       <c r="K20" s="39" t="n">
-        <v>22647341</v>
+        <v>304803612</v>
       </c>
       <c r="L20" s="36" t="inlineStr">
         <is>
@@ -1659,18 +1685,18 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B21" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>2/20</t>
         </is>
       </c>
       <c r="D21" s="36" t="n">
-        <v>146.65</v>
+        <v>130.41</v>
       </c>
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="13" t="n"/>
@@ -1679,20 +1705,30 @@
       <c r="I21" s="13" t="n"/>
       <c r="J21" s="37" t="inlineStr">
         <is>
-          <t>גל ענת</t>
+          <t>פרץ יצחק</t>
         </is>
       </c>
       <c r="K21" s="39" t="n">
-        <v>55740849</v>
+        <v>62041462</v>
       </c>
       <c r="L21" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M21" s="36" t="inlineStr"/>
-      <c r="N21" s="36" t="inlineStr"/>
-      <c r="O21" s="13" t="n"/>
+      <c r="M21" s="36" t="inlineStr">
+        <is>
+          <t>פרץ שרה</t>
+        </is>
+      </c>
+      <c r="N21" s="36" t="n">
+        <v>64570260</v>
+      </c>
+      <c r="O21" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P21" s="16" t="n"/>
       <c r="Q21" s="13" t="n"/>
       <c r="R21" s="13" t="n"/>
@@ -1707,18 +1743,18 @@
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B22" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>17/21</t>
+          <t>2/21</t>
         </is>
       </c>
       <c r="D22" s="36" t="n">
-        <v>128.15</v>
+        <v>127.14</v>
       </c>
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="n"/>
@@ -1727,30 +1763,20 @@
       <c r="I22" s="13" t="n"/>
       <c r="J22" s="39" t="inlineStr">
         <is>
-          <t>הרוש סיון</t>
+          <t>שעיה אופק</t>
         </is>
       </c>
       <c r="K22" s="39" t="n">
-        <v>203341292</v>
+        <v>209438183</v>
       </c>
       <c r="L22" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M22" s="36" t="inlineStr">
-        <is>
-          <t>הרוש עמית</t>
-        </is>
-      </c>
-      <c r="N22" s="36" t="n">
-        <v>203436662</v>
-      </c>
-      <c r="O22" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="M22" s="36" t="inlineStr"/>
+      <c r="N22" s="36" t="inlineStr"/>
+      <c r="O22" s="13" t="n"/>
       <c r="P22" s="16" t="n"/>
       <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
@@ -1765,18 +1791,18 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B23" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>17/22</t>
+          <t>2/22</t>
         </is>
       </c>
       <c r="D23" s="36" t="n">
-        <v>119.15</v>
+        <v>163.84</v>
       </c>
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
@@ -1785,20 +1811,30 @@
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="39" t="inlineStr">
         <is>
-          <t>גמליאלי מוני</t>
+          <t>גנקין נתן</t>
         </is>
       </c>
       <c r="K23" s="39" t="n">
-        <v>41067513</v>
+        <v>307666990</v>
       </c>
       <c r="L23" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M23" s="36" t="inlineStr"/>
-      <c r="N23" s="36" t="inlineStr"/>
-      <c r="O23" s="13" t="n"/>
+      <c r="M23" s="36" t="inlineStr">
+        <is>
+          <t>גנקין יוליה</t>
+        </is>
+      </c>
+      <c r="N23" s="36" t="n">
+        <v>312707995</v>
+      </c>
+      <c r="O23" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P23" s="16" t="n"/>
       <c r="Q23" s="13" t="n"/>
       <c r="R23" s="13" t="n"/>
@@ -1813,18 +1849,18 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B24" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>17/23</t>
+          <t>2/23</t>
         </is>
       </c>
       <c r="D24" s="36" t="n">
-        <v>141.75</v>
+        <v>111.68</v>
       </c>
       <c r="E24" s="13" t="n"/>
       <c r="F24" s="13" t="n"/>
@@ -1833,20 +1869,30 @@
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="39" t="inlineStr">
         <is>
-          <t>שילוח שלומי</t>
+          <t>כהן חי</t>
         </is>
       </c>
       <c r="K24" s="39" t="n">
-        <v>303084826</v>
+        <v>55856785</v>
       </c>
       <c r="L24" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M24" s="36" t="inlineStr"/>
-      <c r="N24" s="36" t="inlineStr"/>
-      <c r="O24" s="13" t="n"/>
+      <c r="M24" s="36" t="inlineStr">
+        <is>
+          <t>כהן אירית</t>
+        </is>
+      </c>
+      <c r="N24" s="36" t="n">
+        <v>58782889</v>
+      </c>
+      <c r="O24" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P24" s="16" t="n"/>
       <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
@@ -1861,18 +1907,18 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B25" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
-          <t>17/24</t>
+          <t>2/24</t>
         </is>
       </c>
       <c r="D25" s="36" t="n">
-        <v>90.95</v>
+        <v>109.82</v>
       </c>
       <c r="E25" s="13" t="n"/>
       <c r="F25" s="13" t="n"/>
@@ -1881,11 +1927,11 @@
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="39" t="inlineStr">
         <is>
-          <t>אלטיט רוני</t>
+          <t>קורקין ניר יחיאל</t>
         </is>
       </c>
       <c r="K25" s="39" t="n">
-        <v>203011788</v>
+        <v>203124227</v>
       </c>
       <c r="L25" s="36" t="inlineStr">
         <is>
@@ -1909,18 +1955,18 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B26" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C26" s="36" t="inlineStr">
         <is>
-          <t>17/25</t>
+          <t>2/25</t>
         </is>
       </c>
       <c r="D26" s="36" t="n">
-        <v>146.65</v>
+        <v>127.14</v>
       </c>
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="n"/>
@@ -1929,20 +1975,30 @@
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="39" t="inlineStr">
         <is>
-          <t>סיני דנה</t>
+          <t>בן שבת הרצל</t>
         </is>
       </c>
       <c r="K26" s="39" t="n">
-        <v>205482995</v>
+        <v>58784505</v>
       </c>
       <c r="L26" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M26" s="36" t="inlineStr"/>
-      <c r="N26" s="36" t="inlineStr"/>
-      <c r="O26" s="13" t="n"/>
+      <c r="M26" s="36" t="inlineStr">
+        <is>
+          <t>בן שבת ג'ואל</t>
+        </is>
+      </c>
+      <c r="N26" s="36" t="n">
+        <v>23783343</v>
+      </c>
+      <c r="O26" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P26" s="16" t="n"/>
       <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
@@ -1957,18 +2013,18 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B27" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>2/26</t>
         </is>
       </c>
       <c r="D27" s="36" t="n">
-        <v>128.15</v>
+        <v>111.44</v>
       </c>
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
@@ -1977,20 +2033,30 @@
       <c r="I27" s="13" t="n"/>
       <c r="J27" s="39" t="inlineStr">
         <is>
-          <t>משען איילת</t>
+          <t>אביב מתן</t>
         </is>
       </c>
       <c r="K27" s="39" t="n">
-        <v>33155789</v>
+        <v>312195795</v>
       </c>
       <c r="L27" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M27" s="36" t="inlineStr"/>
-      <c r="N27" s="36" t="inlineStr"/>
-      <c r="O27" s="13" t="n"/>
+      <c r="M27" s="36" t="inlineStr">
+        <is>
+          <t>אביב מריה</t>
+        </is>
+      </c>
+      <c r="N27" s="36" t="n">
+        <v>321187304</v>
+      </c>
+      <c r="O27" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P27" s="16" t="n"/>
       <c r="Q27" s="13" t="n"/>
       <c r="R27" s="13" t="n"/>
@@ -2005,18 +2071,18 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B28" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>2/27</t>
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>119.15</v>
+        <v>127.14</v>
       </c>
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="13" t="n"/>
@@ -2025,11 +2091,11 @@
       <c r="I28" s="13" t="n"/>
       <c r="J28" s="37" t="inlineStr">
         <is>
-          <t>עבדו אבי</t>
+          <t>שקד מישל</t>
         </is>
       </c>
       <c r="K28" s="39" t="n">
-        <v>203013958</v>
+        <v>38321501</v>
       </c>
       <c r="L28" s="36" t="inlineStr">
         <is>
@@ -2038,11 +2104,11 @@
       </c>
       <c r="M28" s="36" t="inlineStr">
         <is>
-          <t>עבדו נופר</t>
+          <t>איתח שקד שירה</t>
         </is>
       </c>
       <c r="N28" s="36" t="n">
-        <v>304918618</v>
+        <v>39206073</v>
       </c>
       <c r="O28" s="36" t="inlineStr">
         <is>
@@ -2063,18 +2129,18 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B29" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>2/28</t>
         </is>
       </c>
       <c r="D29" s="36" t="n">
-        <v>141.75</v>
+        <v>111.44</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -2083,24 +2149,20 @@
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="39" t="inlineStr">
         <is>
-          <t>אסייהין פנטהון</t>
+          <t>אוחנה לינור</t>
         </is>
       </c>
       <c r="K29" s="39" t="n">
-        <v>323700757</v>
+        <v>308092105</v>
       </c>
       <c r="L29" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="M29" s="36" t="inlineStr"/>
       <c r="N29" s="36" t="inlineStr"/>
-      <c r="O29" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="O29" s="13" t="n"/>
       <c r="P29" s="16" t="n"/>
       <c r="Q29" s="13" t="n"/>
       <c r="R29" s="19" t="n"/>
@@ -2115,18 +2177,18 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B30" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>2/29</t>
         </is>
       </c>
       <c r="D30" s="36" t="n">
-        <v>90.95</v>
+        <v>127.14</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -2135,11 +2197,11 @@
       <c r="I30" s="13" t="n"/>
       <c r="J30" s="39" t="inlineStr">
         <is>
-          <t>לוי לואיזה ליאורה</t>
+          <t>כרמל ארז</t>
         </is>
       </c>
       <c r="K30" s="39" t="n">
-        <v>51357333</v>
+        <v>39349238</v>
       </c>
       <c r="L30" s="36" t="inlineStr">
         <is>
@@ -2163,18 +2225,18 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B31" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>2/30</t>
         </is>
       </c>
       <c r="D31" s="36" t="n">
-        <v>134.5</v>
+        <v>111.44</v>
       </c>
       <c r="E31" s="13" t="n"/>
       <c r="F31" s="13" t="n"/>
@@ -2183,20 +2245,30 @@
       <c r="I31" s="13" t="n"/>
       <c r="J31" s="39" t="inlineStr">
         <is>
-          <t>עינב נעמה</t>
+          <t>קניגין אנטולי</t>
         </is>
       </c>
       <c r="K31" s="39" t="n">
-        <v>203798491</v>
+        <v>312686819</v>
       </c>
       <c r="L31" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M31" s="36" t="inlineStr"/>
-      <c r="N31" s="36" t="inlineStr"/>
-      <c r="O31" s="13" t="n"/>
+      <c r="M31" s="36" t="inlineStr">
+        <is>
+          <t>קניגין ולנטינה</t>
+        </is>
+      </c>
+      <c r="N31" s="36" t="n">
+        <v>320969199</v>
+      </c>
+      <c r="O31" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P31" s="16" t="n"/>
       <c r="Q31" s="13" t="n"/>
       <c r="R31" s="13" t="n"/>
@@ -2211,18 +2283,18 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B32" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>2/31</t>
         </is>
       </c>
       <c r="D32" s="36" t="n">
-        <v>128.15</v>
+        <v>127.14</v>
       </c>
       <c r="E32" s="13" t="n"/>
       <c r="F32" s="13" t="n"/>
@@ -2231,11 +2303,11 @@
       <c r="I32" s="13" t="n"/>
       <c r="J32" s="39" t="inlineStr">
         <is>
-          <t>בשרי לי</t>
+          <t>דיטשי אורית</t>
         </is>
       </c>
       <c r="K32" s="39" t="n">
-        <v>203905922</v>
+        <v>200297679</v>
       </c>
       <c r="L32" s="36" t="inlineStr">
         <is>
@@ -2244,11 +2316,11 @@
       </c>
       <c r="M32" s="36" t="inlineStr">
         <is>
-          <t>בשרי עידו</t>
+          <t>סגרון עידן</t>
         </is>
       </c>
       <c r="N32" s="36" t="n">
-        <v>37084506</v>
+        <v>36965556</v>
       </c>
       <c r="O32" s="36" t="inlineStr">
         <is>
@@ -2269,18 +2341,18 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B33" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>17/32</t>
+          <t>2/32</t>
         </is>
       </c>
       <c r="D33" s="36" t="n">
-        <v>119.45</v>
+        <v>111.44</v>
       </c>
       <c r="E33" s="13" t="n"/>
       <c r="F33" s="13" t="n"/>
@@ -2289,19 +2361,25 @@
       <c r="I33" s="13" t="n"/>
       <c r="J33" s="39" t="inlineStr">
         <is>
-          <t>נעים ניצן</t>
+          <t>סויסה עליזה</t>
         </is>
       </c>
       <c r="K33" s="39" t="n">
-        <v>315008755</v>
+        <v>54105481</v>
       </c>
       <c r="L33" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M33" s="36" t="inlineStr"/>
-      <c r="N33" s="36" t="inlineStr"/>
+      <c r="M33" s="36" t="inlineStr">
+        <is>
+          <t>סויסה ארמנד</t>
+        </is>
+      </c>
+      <c r="N33" s="36" t="n">
+        <v>69685287</v>
+      </c>
       <c r="O33" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -2321,18 +2399,18 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B34" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>17/33</t>
+          <t>2/33</t>
         </is>
       </c>
       <c r="D34" s="36" t="n">
-        <v>141.95</v>
+        <v>127.14</v>
       </c>
       <c r="E34" s="13" t="n"/>
       <c r="F34" s="13" t="n"/>
@@ -2341,19 +2419,25 @@
       <c r="I34" s="13" t="n"/>
       <c r="J34" s="39" t="inlineStr">
         <is>
-          <t>קויאט איתן יוסף</t>
+          <t>ניר איתי</t>
         </is>
       </c>
       <c r="K34" s="39" t="n">
-        <v>34410837</v>
+        <v>66744657</v>
       </c>
       <c r="L34" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M34" s="36" t="inlineStr"/>
-      <c r="N34" s="36" t="inlineStr"/>
+      <c r="M34" s="36" t="inlineStr">
+        <is>
+          <t>ניר דניאלה</t>
+        </is>
+      </c>
+      <c r="N34" s="36" t="n">
+        <v>36954402</v>
+      </c>
       <c r="O34" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -2373,18 +2457,18 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B35" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>17/34</t>
+          <t>2/34</t>
         </is>
       </c>
       <c r="D35" s="36" t="n">
-        <v>126.75</v>
+        <v>130.41</v>
       </c>
       <c r="E35" s="13" t="n"/>
       <c r="F35" s="13" t="n"/>
@@ -2393,20 +2477,30 @@
       <c r="I35" s="13" t="n"/>
       <c r="J35" s="39" t="inlineStr">
         <is>
-          <t>נוף דוד</t>
+          <t>סדיחוב דיאנה</t>
         </is>
       </c>
       <c r="K35" s="39" t="n">
-        <v>31387657</v>
+        <v>314470113</v>
       </c>
       <c r="L35" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M35" s="36" t="inlineStr"/>
-      <c r="N35" s="36" t="inlineStr"/>
-      <c r="O35" s="13" t="n"/>
+      <c r="M35" s="36" t="inlineStr">
+        <is>
+          <t>סדיחוב אוהד</t>
+        </is>
+      </c>
+      <c r="N35" s="36" t="n">
+        <v>314470089</v>
+      </c>
+      <c r="O35" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P35" s="16" t="n"/>
       <c r="Q35" s="13" t="n"/>
       <c r="R35" s="13" t="n"/>
@@ -2421,18 +2515,18 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B36" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>17/35</t>
+          <t>2/35</t>
         </is>
       </c>
       <c r="D36" s="36" t="n">
-        <v>149.05</v>
+        <v>163.84</v>
       </c>
       <c r="E36" s="13" t="n"/>
       <c r="F36" s="13" t="n"/>
@@ -2441,11 +2535,11 @@
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="39" t="inlineStr">
         <is>
-          <t>חממי אביב</t>
+          <t>אלעטאונה דוגאן</t>
         </is>
       </c>
       <c r="K36" s="39" t="n">
-        <v>60409190</v>
+        <v>52457702</v>
       </c>
       <c r="L36" s="36" t="inlineStr">
         <is>
@@ -2454,11 +2548,11 @@
       </c>
       <c r="M36" s="36" t="inlineStr">
         <is>
-          <t>חממי שירן</t>
+          <t>אלעטאונה סנא</t>
         </is>
       </c>
       <c r="N36" s="36" t="n">
-        <v>36923019</v>
+        <v>27605161</v>
       </c>
       <c r="O36" s="36" t="inlineStr">
         <is>
@@ -2478,18 +2572,18 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B37" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>17/36</t>
+          <t>2/36</t>
         </is>
       </c>
       <c r="D37" s="36" t="n">
-        <v>119.15</v>
+        <v>105.03</v>
       </c>
       <c r="E37" s="13" t="n"/>
       <c r="F37" s="13" t="n"/>
@@ -2498,11 +2592,11 @@
       <c r="I37" s="13" t="n"/>
       <c r="J37" s="39" t="inlineStr">
         <is>
-          <t>חביב מנשה</t>
+          <t>דוד שגיב</t>
         </is>
       </c>
       <c r="K37" s="39" t="n">
-        <v>54375852</v>
+        <v>21526777</v>
       </c>
       <c r="L37" s="36" t="inlineStr">
         <is>
@@ -2511,11 +2605,11 @@
       </c>
       <c r="M37" s="36" t="inlineStr">
         <is>
-          <t>חביב פנינה</t>
+          <t>דוד חן</t>
         </is>
       </c>
       <c r="N37" s="36" t="n">
-        <v>50820190</v>
+        <v>300831880</v>
       </c>
       <c r="O37" s="36" t="inlineStr">
         <is>
@@ -2536,18 +2630,18 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B38" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C38" s="36" t="inlineStr">
         <is>
-          <t>17/37</t>
+          <t>2/37</t>
         </is>
       </c>
       <c r="D38" s="36" t="n">
-        <v>141.6</v>
+        <v>104.13</v>
       </c>
       <c r="E38" s="13" t="n"/>
       <c r="F38" s="13" t="n"/>
@@ -2556,30 +2650,20 @@
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="39" t="inlineStr">
         <is>
-          <t>כהן אופיר</t>
+          <t>לוי רוזי ורדה</t>
         </is>
       </c>
       <c r="K38" s="39" t="n">
-        <v>29532025</v>
+        <v>25677774</v>
       </c>
       <c r="L38" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M38" s="36" t="inlineStr">
-        <is>
-          <t>כהן שרונה</t>
-        </is>
-      </c>
-      <c r="N38" s="36" t="n">
-        <v>33526070</v>
-      </c>
-      <c r="O38" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="M38" s="36" t="inlineStr"/>
+      <c r="N38" s="36" t="inlineStr"/>
+      <c r="O38" s="13" t="n"/>
       <c r="P38" s="13" t="n"/>
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
@@ -2594,18 +2678,18 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B39" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>17/38</t>
+          <t>2/38</t>
         </is>
       </c>
       <c r="D39" s="36" t="n">
-        <v>131.6</v>
+        <v>105.36</v>
       </c>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="13" t="n"/>
@@ -2614,11 +2698,11 @@
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="39" t="inlineStr">
         <is>
-          <t>בלושיצקי פולינה</t>
+          <t>איטח שמעון נועם</t>
         </is>
       </c>
       <c r="K39" s="39" t="n">
-        <v>304113756</v>
+        <v>308202530</v>
       </c>
       <c r="L39" s="36" t="inlineStr">
         <is>
@@ -2642,18 +2726,18 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B40" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>17/39</t>
+          <t>2/39</t>
         </is>
       </c>
       <c r="D40" s="36" t="n">
-        <v>148.75</v>
+        <v>104.49</v>
       </c>
       <c r="E40" s="13" t="n"/>
       <c r="F40" s="13" t="n"/>
@@ -2662,20 +2746,30 @@
       <c r="I40" s="13" t="n"/>
       <c r="J40" s="39" t="inlineStr">
         <is>
-          <t>יערי עומר</t>
+          <t>אבי מאור</t>
         </is>
       </c>
       <c r="K40" s="39" t="n">
-        <v>312472335</v>
+        <v>200827095</v>
       </c>
       <c r="L40" s="36" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/2</t>
         </is>
       </c>
-      <c r="M40" s="36" t="inlineStr"/>
-      <c r="N40" s="36" t="inlineStr"/>
-      <c r="O40" s="13" t="n"/>
+      <c r="M40" s="36" t="inlineStr">
+        <is>
+          <t>זנד אבי טל</t>
+        </is>
+      </c>
+      <c r="N40" s="36" t="n">
+        <v>302188719</v>
+      </c>
+      <c r="O40" s="36" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="P40" s="13" t="n"/>
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
@@ -2690,18 +2784,18 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B41" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>17/40</t>
+          <t>2/40</t>
         </is>
       </c>
       <c r="D41" s="36" t="n">
-        <v>119.15</v>
+        <v>105.36</v>
       </c>
       <c r="E41" s="13" t="n"/>
       <c r="F41" s="13" t="n"/>
@@ -2710,30 +2804,20 @@
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="39" t="inlineStr">
         <is>
-          <t>שלם ענבל</t>
+          <t>ביטון אוהד</t>
         </is>
       </c>
       <c r="K41" s="39" t="n">
-        <v>37992682</v>
+        <v>303021380</v>
       </c>
       <c r="L41" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M41" s="36" t="inlineStr">
-        <is>
-          <t>שלם ענבל</t>
-        </is>
-      </c>
-      <c r="N41" s="36" t="n">
-        <v>37992682</v>
-      </c>
-      <c r="O41" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="M41" s="36" t="inlineStr"/>
+      <c r="N41" s="36" t="inlineStr"/>
+      <c r="O41" s="13" t="n"/>
       <c r="P41" s="13" t="n"/>
       <c r="Q41" s="13" t="n"/>
       <c r="R41" s="13" t="n"/>
@@ -2748,18 +2832,18 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B42" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>17/41</t>
+          <t>2/41</t>
         </is>
       </c>
       <c r="D42" s="36" t="n">
-        <v>141.6</v>
+        <v>104.49</v>
       </c>
       <c r="E42" s="13" t="n"/>
       <c r="F42" s="13" t="n"/>
@@ -2768,24 +2852,20 @@
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="39" t="inlineStr">
         <is>
-          <t>טייטלבום צבי זאב ליאור</t>
+          <t>פוחיס ליאת</t>
         </is>
       </c>
       <c r="K42" s="39" t="n">
-        <v>58087594</v>
+        <v>207216722</v>
       </c>
       <c r="L42" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="M42" s="36" t="inlineStr"/>
       <c r="N42" s="36" t="inlineStr"/>
-      <c r="O42" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="O42" s="13" t="n"/>
       <c r="P42" s="13" t="n"/>
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
@@ -2800,18 +2880,18 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B43" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>17/42</t>
+          <t>2/42</t>
         </is>
       </c>
       <c r="D43" s="36" t="n">
-        <v>131.6</v>
+        <v>105.36</v>
       </c>
       <c r="E43" s="13" t="n"/>
       <c r="F43" s="13" t="n"/>
@@ -2820,30 +2900,20 @@
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="39" t="inlineStr">
         <is>
-          <t>לביא פלדמן לאורה</t>
+          <t>קאבר אריה</t>
         </is>
       </c>
       <c r="K43" s="39" t="n">
-        <v>11769007</v>
+        <v>52036498</v>
       </c>
       <c r="L43" s="36" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/1</t>
         </is>
       </c>
-      <c r="M43" s="36" t="inlineStr">
-        <is>
-          <t>פלדמן עופר יששכר</t>
-        </is>
-      </c>
-      <c r="N43" s="36" t="n">
-        <v>57982555</v>
-      </c>
-      <c r="O43" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="M43" s="36" t="inlineStr"/>
+      <c r="N43" s="36" t="inlineStr"/>
+      <c r="O43" s="13" t="n"/>
       <c r="P43" s="13" t="n"/>
       <c r="Q43" s="13" t="n"/>
       <c r="R43" s="13" t="n"/>
@@ -2858,18 +2928,18 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B44" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C44" s="36" t="inlineStr">
         <is>
-          <t>17/43</t>
+          <t>2/43</t>
         </is>
       </c>
       <c r="D44" s="36" t="n">
-        <v>148.75</v>
+        <v>104.49</v>
       </c>
       <c r="E44" s="13" t="n"/>
       <c r="F44" s="13" t="n"/>
@@ -2878,19 +2948,25 @@
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="39" t="inlineStr">
         <is>
-          <t>לוי אלה</t>
+          <t>פרץ סלבי</t>
         </is>
       </c>
       <c r="K44" s="39" t="n">
-        <v>38213435</v>
+        <v>14305866</v>
       </c>
       <c r="L44" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="M44" s="36" t="inlineStr"/>
-      <c r="N44" s="36" t="inlineStr"/>
+      <c r="M44" s="36" t="inlineStr">
+        <is>
+          <t>פרץ מישל</t>
+        </is>
+      </c>
+      <c r="N44" s="36" t="n">
+        <v>69174704</v>
+      </c>
       <c r="O44" s="36" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -2910,18 +2986,18 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>7284</v>
+        <v>38364</v>
       </c>
       <c r="B45" s="36" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C45" s="36" t="inlineStr">
         <is>
-          <t>17/44</t>
+          <t>2/44</t>
         </is>
       </c>
       <c r="D45" s="36" t="n">
-        <v>119.15</v>
+        <v>150.33</v>
       </c>
       <c r="E45" s="13" t="n"/>
       <c r="F45" s="13" t="n"/>
@@ -2930,15 +3006,15 @@
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="39" t="inlineStr">
         <is>
-          <t>עבדו אוריה</t>
+          <t>לארדו מרדכי</t>
         </is>
       </c>
       <c r="K45" s="39" t="n">
-        <v>302818307</v>
+        <v>31927551</v>
       </c>
       <c r="L45" s="36" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="M45" s="36" t="inlineStr"/>
@@ -2957,51 +3033,21 @@
       <c r="Z45" s="1" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B46" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C46" s="36" t="inlineStr">
-        <is>
-          <t>17/45</t>
-        </is>
-      </c>
-      <c r="D46" s="36" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
       <c r="E46" s="13" t="n"/>
       <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
       <c r="H46" s="13" t="n"/>
       <c r="I46" s="13" t="n"/>
-      <c r="J46" s="39" t="inlineStr">
-        <is>
-          <t>דסה אז'מלש הדר</t>
-        </is>
-      </c>
-      <c r="K46" s="39" t="n">
-        <v>15914096</v>
-      </c>
-      <c r="L46" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M46" s="36" t="inlineStr">
-        <is>
-          <t>דסה סיסאי</t>
-        </is>
-      </c>
-      <c r="N46" s="36" t="n">
-        <v>15932072</v>
-      </c>
-      <c r="O46" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="29" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="13" t="n"/>
       <c r="P46" s="13" t="n"/>
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
@@ -3015,45 +3061,21 @@
       <c r="Z46" s="1" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B47" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C47" s="36" t="inlineStr">
-        <is>
-          <t>17/46</t>
-        </is>
-      </c>
-      <c r="D47" s="36" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
       <c r="E47" s="13" t="n"/>
       <c r="F47" s="13" t="n"/>
       <c r="G47" s="13" t="n"/>
       <c r="H47" s="13" t="n"/>
       <c r="I47" s="13" t="n"/>
-      <c r="J47" s="39" t="inlineStr">
-        <is>
-          <t>רוזמרין רונלי</t>
-        </is>
-      </c>
-      <c r="K47" s="39" t="n">
-        <v>40837395</v>
-      </c>
-      <c r="L47" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M47" s="36" t="inlineStr"/>
-      <c r="N47" s="36" t="inlineStr"/>
-      <c r="O47" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J47" s="29" t="n"/>
+      <c r="K47" s="29" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
       <c r="P47" s="13" t="n"/>
       <c r="Q47" s="13" t="n"/>
       <c r="R47" s="13" t="n"/>
@@ -3067,42 +3089,20 @@
       <c r="Z47" s="1" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B48" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C48" s="36" t="inlineStr">
-        <is>
-          <t>17/47</t>
-        </is>
-      </c>
-      <c r="D48" s="36" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
       <c r="E48" s="13" t="n"/>
       <c r="F48" s="13" t="n"/>
       <c r="G48" s="13" t="n"/>
       <c r="H48" s="13" t="n"/>
       <c r="I48" s="13" t="n"/>
-      <c r="J48" s="39" t="inlineStr">
-        <is>
-          <t>גנה אלה</t>
-        </is>
-      </c>
-      <c r="K48" s="39" t="n">
-        <v>303878870</v>
-      </c>
-      <c r="L48" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M48" s="36" t="inlineStr"/>
-      <c r="N48" s="36" t="inlineStr"/>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="29" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
       <c r="P48" s="13" t="n"/>
       <c r="Q48" s="13" t="n"/>
@@ -3117,45 +3117,21 @@
       <c r="Z48" s="1" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B49" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C49" s="36" t="inlineStr">
-        <is>
-          <t>17/48</t>
-        </is>
-      </c>
-      <c r="D49" s="36" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
       <c r="E49" s="13" t="n"/>
       <c r="F49" s="13" t="n"/>
       <c r="G49" s="13" t="n"/>
       <c r="H49" s="13" t="n"/>
       <c r="I49" s="13" t="n"/>
-      <c r="J49" s="39" t="inlineStr">
-        <is>
-          <t>פלד עמוס</t>
-        </is>
-      </c>
-      <c r="K49" s="39" t="n">
-        <v>203246269</v>
-      </c>
-      <c r="L49" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M49" s="36" t="inlineStr"/>
-      <c r="N49" s="36" t="inlineStr"/>
-      <c r="O49" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J49" s="29" t="n"/>
+      <c r="K49" s="29" t="n"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="13" t="n"/>
+      <c r="N49" s="13" t="n"/>
+      <c r="O49" s="13" t="n"/>
       <c r="P49" s="13" t="n"/>
       <c r="Q49" s="13" t="n"/>
       <c r="R49" s="13" t="n"/>
@@ -3169,51 +3145,21 @@
       <c r="Z49" s="1" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B50" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" s="36" t="inlineStr">
-        <is>
-          <t>17/49</t>
-        </is>
-      </c>
-      <c r="D50" s="36" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
       <c r="E50" s="13" t="n"/>
       <c r="F50" s="13" t="n"/>
       <c r="G50" s="13" t="n"/>
       <c r="H50" s="13" t="n"/>
       <c r="I50" s="13" t="n"/>
-      <c r="J50" s="39" t="inlineStr">
-        <is>
-          <t>בוליס חיים יפים</t>
-        </is>
-      </c>
-      <c r="K50" s="39" t="n">
-        <v>16741720</v>
-      </c>
-      <c r="L50" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M50" s="36" t="inlineStr">
-        <is>
-          <t>חלה בוליס אסנת</t>
-        </is>
-      </c>
-      <c r="N50" s="36" t="n">
-        <v>34251082</v>
-      </c>
-      <c r="O50" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="29" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="13" t="n"/>
       <c r="P50" s="13" t="n"/>
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
@@ -3227,40 +3173,20 @@
       <c r="Z50" s="1" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B51" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="36" t="inlineStr">
-        <is>
-          <t>17/50</t>
-        </is>
-      </c>
-      <c r="D51" s="36" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
       <c r="E51" s="13" t="n"/>
       <c r="F51" s="13" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="13" t="n"/>
       <c r="I51" s="13" t="n"/>
-      <c r="J51" s="39" t="inlineStr">
-        <is>
-          <t>גן ברוך יצחק</t>
-        </is>
-      </c>
-      <c r="K51" s="39" t="n">
-        <v>29637881</v>
-      </c>
-      <c r="L51" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M51" s="36" t="inlineStr"/>
-      <c r="N51" s="36" t="inlineStr"/>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="29" t="n"/>
+      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="13" t="n"/>
+      <c r="N51" s="13" t="n"/>
       <c r="O51" s="13" t="n"/>
       <c r="P51" s="13" t="n"/>
       <c r="Q51" s="13" t="n"/>
@@ -3275,42 +3201,20 @@
       <c r="Z51" s="1" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B52" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C52" s="36" t="inlineStr">
-        <is>
-          <t>17/51</t>
-        </is>
-      </c>
-      <c r="D52" s="36" t="n">
-        <v>148.75</v>
-      </c>
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="13" t="n"/>
+      <c r="C52" s="13" t="n"/>
+      <c r="D52" s="13" t="n"/>
       <c r="E52" s="13" t="n"/>
       <c r="F52" s="13" t="n"/>
       <c r="G52" s="13" t="n"/>
       <c r="H52" s="13" t="n"/>
       <c r="I52" s="13" t="n"/>
-      <c r="J52" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K52" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L52" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M52" s="36" t="inlineStr"/>
-      <c r="N52" s="36" t="inlineStr"/>
+      <c r="J52" s="29" t="n"/>
+      <c r="K52" s="29" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
       <c r="P52" s="13" t="n"/>
       <c r="Q52" s="13" t="n"/>
@@ -3325,40 +3229,20 @@
       <c r="Z52" s="1" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B53" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C53" s="36" t="inlineStr">
-        <is>
-          <t>17/52</t>
-        </is>
-      </c>
-      <c r="D53" s="36" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
       <c r="E53" s="13" t="n"/>
       <c r="F53" s="13" t="n"/>
       <c r="G53" s="13" t="n"/>
       <c r="H53" s="13" t="n"/>
       <c r="I53" s="13" t="n"/>
-      <c r="J53" s="39" t="inlineStr">
-        <is>
-          <t>דניאל גיא</t>
-        </is>
-      </c>
-      <c r="K53" s="39" t="n">
-        <v>312127228</v>
-      </c>
-      <c r="L53" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M53" s="36" t="inlineStr"/>
-      <c r="N53" s="36" t="inlineStr"/>
+      <c r="J53" s="29" t="n"/>
+      <c r="K53" s="29" t="n"/>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="13" t="n"/>
+      <c r="N53" s="13" t="n"/>
       <c r="O53" s="13" t="n"/>
       <c r="P53" s="13" t="n"/>
       <c r="Q53" s="13" t="n"/>
@@ -3373,42 +3257,20 @@
       <c r="Z53" s="1" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B54" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C54" s="36" t="inlineStr">
-        <is>
-          <t>17/53</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
       <c r="E54" s="13" t="n"/>
       <c r="F54" s="13" t="n"/>
       <c r="G54" s="13" t="n"/>
       <c r="H54" s="13" t="n"/>
       <c r="I54" s="13" t="n"/>
-      <c r="J54" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K54" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L54" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M54" s="36" t="inlineStr"/>
-      <c r="N54" s="36" t="inlineStr"/>
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="29" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="13" t="n"/>
@@ -3423,51 +3285,21 @@
       <c r="Z54" s="1" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B55" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C55" s="36" t="inlineStr">
-        <is>
-          <t>17/54</t>
-        </is>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
       <c r="E55" s="13" t="n"/>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
       <c r="I55" s="13" t="n"/>
-      <c r="J55" s="39" t="inlineStr">
-        <is>
-          <t>שולמן יורי</t>
-        </is>
-      </c>
-      <c r="K55" s="39" t="n">
-        <v>306059361</v>
-      </c>
-      <c r="L55" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M55" s="36" t="inlineStr">
-        <is>
-          <t>ויניצקי אילנה</t>
-        </is>
-      </c>
-      <c r="N55" s="36" t="n">
-        <v>305151581</v>
-      </c>
-      <c r="O55" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J55" s="29" t="n"/>
+      <c r="K55" s="29" t="n"/>
+      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="13" t="n"/>
+      <c r="N55" s="13" t="n"/>
+      <c r="O55" s="13" t="n"/>
       <c r="P55" s="13" t="n"/>
       <c r="Q55" s="13" t="n"/>
       <c r="R55" s="13" t="n"/>
@@ -3481,45 +3313,21 @@
       <c r="Z55" s="1" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B56" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C56" s="36" t="inlineStr">
-        <is>
-          <t>17/55</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="n">
-        <v>148.75</v>
-      </c>
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
       <c r="E56" s="13" t="n"/>
       <c r="F56" s="13" t="n"/>
       <c r="G56" s="13" t="n"/>
       <c r="H56" s="13" t="n"/>
       <c r="I56" s="13" t="n"/>
-      <c r="J56" s="39" t="inlineStr">
-        <is>
-          <t>פורמן גל</t>
-        </is>
-      </c>
-      <c r="K56" s="39" t="n">
-        <v>318866241</v>
-      </c>
-      <c r="L56" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M56" s="36" t="inlineStr"/>
-      <c r="N56" s="36" t="inlineStr"/>
-      <c r="O56" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J56" s="29" t="n"/>
+      <c r="K56" s="29" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="13" t="n"/>
+      <c r="O56" s="13" t="n"/>
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
@@ -3533,40 +3341,20 @@
       <c r="Z56" s="1" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B57" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C57" s="36" t="inlineStr">
-        <is>
-          <t>17/56</t>
-        </is>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
       <c r="E57" s="13" t="n"/>
       <c r="F57" s="13" t="n"/>
       <c r="G57" s="13" t="n"/>
       <c r="H57" s="13" t="n"/>
       <c r="I57" s="13" t="n"/>
-      <c r="J57" s="39" t="inlineStr">
-        <is>
-          <t>שקולניק עידו</t>
-        </is>
-      </c>
-      <c r="K57" s="39" t="n">
-        <v>302844337</v>
-      </c>
-      <c r="L57" s="36" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="M57" s="36" t="inlineStr"/>
-      <c r="N57" s="36" t="inlineStr"/>
+      <c r="J57" s="29" t="n"/>
+      <c r="K57" s="29" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="13" t="n"/>
+      <c r="N57" s="13" t="n"/>
       <c r="O57" s="13" t="n"/>
       <c r="P57" s="13" t="n"/>
       <c r="Q57" s="13" t="n"/>
@@ -3581,42 +3369,20 @@
       <c r="Z57" s="1" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B58" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C58" s="36" t="inlineStr">
-        <is>
-          <t>17/57</t>
-        </is>
-      </c>
-      <c r="D58" s="36" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
       <c r="E58" s="13" t="n"/>
       <c r="F58" s="13" t="n"/>
       <c r="G58" s="13" t="n"/>
       <c r="H58" s="13" t="n"/>
       <c r="I58" s="13" t="n"/>
-      <c r="J58" s="37" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K58" s="37" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L58" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M58" s="38" t="inlineStr"/>
-      <c r="N58" s="38" t="inlineStr"/>
+      <c r="J58" s="30" t="n"/>
+      <c r="K58" s="30" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="14" t="n"/>
+      <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="13" t="n"/>
       <c r="Q58" s="13" t="n"/>
@@ -3631,51 +3397,21 @@
       <c r="Z58" s="1" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B59" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C59" s="36" t="inlineStr">
-        <is>
-          <t>17/58</t>
-        </is>
-      </c>
-      <c r="D59" s="36" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="13" t="n"/>
       <c r="E59" s="13" t="n"/>
       <c r="F59" s="13" t="n"/>
       <c r="G59" s="13" t="n"/>
       <c r="H59" s="13" t="n"/>
       <c r="I59" s="13" t="n"/>
-      <c r="J59" s="39" t="inlineStr">
-        <is>
-          <t>ויסברג יצחק</t>
-        </is>
-      </c>
-      <c r="K59" s="39" t="n">
-        <v>51047314</v>
-      </c>
-      <c r="L59" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M59" s="36" t="inlineStr">
-        <is>
-          <t>ויסברג פרידה</t>
-        </is>
-      </c>
-      <c r="N59" s="36" t="n">
-        <v>51570299</v>
-      </c>
-      <c r="O59" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J59" s="29" t="n"/>
+      <c r="K59" s="29" t="n"/>
+      <c r="L59" s="13" t="n"/>
+      <c r="M59" s="13" t="n"/>
+      <c r="N59" s="13" t="n"/>
+      <c r="O59" s="13" t="n"/>
       <c r="P59" s="13" t="n"/>
       <c r="Q59" s="13" t="n"/>
       <c r="R59" s="13" t="n"/>
@@ -3689,42 +3425,20 @@
       <c r="Z59" s="1" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B60" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C60" s="36" t="inlineStr">
-        <is>
-          <t>17/59</t>
-        </is>
-      </c>
-      <c r="D60" s="36" t="n">
-        <v>148.75</v>
-      </c>
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
       <c r="E60" s="13" t="n"/>
       <c r="F60" s="13" t="n"/>
       <c r="G60" s="13" t="n"/>
       <c r="H60" s="13" t="n"/>
       <c r="I60" s="13" t="n"/>
-      <c r="J60" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K60" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L60" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M60" s="36" t="inlineStr"/>
-      <c r="N60" s="36" t="inlineStr"/>
+      <c r="J60" s="29" t="n"/>
+      <c r="K60" s="29" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="13" t="n"/>
       <c r="O60" s="13" t="n"/>
       <c r="P60" s="13" t="n"/>
       <c r="Q60" s="13" t="n"/>
@@ -3739,40 +3453,20 @@
       <c r="Z60" s="1" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B61" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C61" s="36" t="inlineStr">
-        <is>
-          <t>17/60</t>
-        </is>
-      </c>
-      <c r="D61" s="36" t="n">
-        <v>107.7</v>
-      </c>
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
       <c r="E61" s="13" t="n"/>
       <c r="F61" s="13" t="n"/>
       <c r="G61" s="13" t="n"/>
       <c r="H61" s="13" t="n"/>
       <c r="I61" s="13" t="n"/>
-      <c r="J61" s="39" t="inlineStr">
-        <is>
-          <t>חרלמוב קלניצקי אלה</t>
-        </is>
-      </c>
-      <c r="K61" s="39" t="n">
-        <v>310194022</v>
-      </c>
-      <c r="L61" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M61" s="36" t="inlineStr"/>
-      <c r="N61" s="36" t="inlineStr"/>
+      <c r="J61" s="29" t="n"/>
+      <c r="K61" s="29" t="n"/>
+      <c r="L61" s="13" t="n"/>
+      <c r="M61" s="13" t="n"/>
+      <c r="N61" s="13" t="n"/>
       <c r="O61" s="13" t="n"/>
       <c r="P61" s="13" t="n"/>
       <c r="Q61" s="13" t="n"/>
@@ -3787,42 +3481,20 @@
       <c r="Z61" s="1" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B62" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C62" s="36" t="inlineStr">
-        <is>
-          <t>17/61</t>
-        </is>
-      </c>
-      <c r="D62" s="36" t="n">
-        <v>129.1</v>
-      </c>
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
       <c r="E62" s="13" t="n"/>
       <c r="F62" s="13" t="n"/>
       <c r="G62" s="13" t="n"/>
       <c r="H62" s="13" t="n"/>
       <c r="I62" s="13" t="n"/>
-      <c r="J62" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K62" s="39" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L62" s="36" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M62" s="36" t="inlineStr"/>
-      <c r="N62" s="36" t="inlineStr"/>
+      <c r="J62" s="29" t="n"/>
+      <c r="K62" s="29" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
       <c r="O62" s="13" t="n"/>
       <c r="P62" s="13" t="n"/>
       <c r="Q62" s="13" t="n"/>
@@ -3837,51 +3509,21 @@
       <c r="Z62" s="1" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="36" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B63" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="C63" s="36" t="inlineStr">
-        <is>
-          <t>17/62</t>
-        </is>
-      </c>
-      <c r="D63" s="36" t="n">
-        <v>119.4</v>
-      </c>
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
       <c r="E63" s="13" t="n"/>
       <c r="F63" s="13" t="n"/>
       <c r="G63" s="13" t="n"/>
       <c r="H63" s="13" t="n"/>
       <c r="I63" s="13" t="n"/>
-      <c r="J63" s="39" t="inlineStr">
-        <is>
-          <t>פיטקובסקי שון</t>
-        </is>
-      </c>
-      <c r="K63" s="39" t="n">
-        <v>204316129</v>
-      </c>
-      <c r="L63" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M63" s="36" t="inlineStr">
-        <is>
-          <t>לוין בר</t>
-        </is>
-      </c>
-      <c r="N63" s="36" t="n">
-        <v>313583650</v>
-      </c>
-      <c r="O63" s="36" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J63" s="29" t="n"/>
+      <c r="K63" s="29" t="n"/>
+      <c r="L63" s="13" t="n"/>
+      <c r="M63" s="13" t="n"/>
+      <c r="N63" s="13" t="n"/>
+      <c r="O63" s="13" t="n"/>
       <c r="P63" s="13" t="n"/>
       <c r="Q63" s="13" t="n"/>
       <c r="R63" s="13" t="n"/>
@@ -3895,42 +3537,20 @@
       <c r="Z63" s="1" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="41" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B64" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>17/63</t>
-        </is>
-      </c>
-      <c r="D64" s="41" t="n">
-        <v>136.25</v>
-      </c>
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
-      <c r="J64" s="42" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K64" s="42" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L64" s="41" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M64" s="41" t="inlineStr"/>
-      <c r="N64" s="41" t="inlineStr"/>
+      <c r="J64" s="31" t="n"/>
+      <c r="K64" s="31" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="7" t="n"/>
       <c r="O64" s="7" t="n"/>
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="7" t="n"/>
@@ -3945,42 +3565,20 @@
       <c r="Z64" s="1" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B65" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C65" s="43" t="inlineStr">
-        <is>
-          <t>17/64</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="n">
-        <v>107.7</v>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
-      <c r="J65" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K65" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L65" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M65" s="43" t="inlineStr"/>
-      <c r="N65" s="43" t="inlineStr"/>
+      <c r="J65" s="32" t="n"/>
+      <c r="K65" s="32" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="n"/>
@@ -3995,42 +3593,20 @@
       <c r="Z65" s="1" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B66" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C66" s="43" t="inlineStr">
-        <is>
-          <t>17/65</t>
-        </is>
-      </c>
-      <c r="D66" s="43" t="n">
-        <v>129.1</v>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
-      <c r="J66" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K66" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L66" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M66" s="43" t="inlineStr"/>
-      <c r="N66" s="43" t="inlineStr"/>
+      <c r="J66" s="32" t="n"/>
+      <c r="K66" s="32" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="n"/>
@@ -4045,51 +3621,21 @@
       <c r="Z66" s="1" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B67" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C67" s="43" t="inlineStr">
-        <is>
-          <t>17/66</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="n">
-        <v>119.4</v>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
-      <c r="J67" s="44" t="inlineStr">
-        <is>
-          <t>בן-שטרית עמית</t>
-        </is>
-      </c>
-      <c r="K67" s="44" t="n">
-        <v>64976954</v>
-      </c>
-      <c r="L67" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M67" s="43" t="inlineStr">
-        <is>
-          <t>מסילאתי בן-שטרית לירון</t>
-        </is>
-      </c>
-      <c r="N67" s="43" t="n">
-        <v>37122165</v>
-      </c>
-      <c r="O67" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J67" s="32" t="n"/>
+      <c r="K67" s="32" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="n"/>
@@ -4103,42 +3649,20 @@
       <c r="Z67" s="1" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B68" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C68" s="43" t="inlineStr">
-        <is>
-          <t>17/67</t>
-        </is>
-      </c>
-      <c r="D68" s="43" t="n">
-        <v>136.25</v>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
-      <c r="J68" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K68" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L68" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M68" s="43" t="inlineStr"/>
-      <c r="N68" s="43" t="inlineStr"/>
+      <c r="J68" s="32" t="n"/>
+      <c r="K68" s="32" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="n"/>
@@ -4153,42 +3677,20 @@
       <c r="Z68" s="1" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B69" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C69" s="43" t="inlineStr">
-        <is>
-          <t>17/68</t>
-        </is>
-      </c>
-      <c r="D69" s="43" t="n">
-        <v>107.7</v>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n"/>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
-      <c r="J69" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K69" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L69" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M69" s="43" t="inlineStr"/>
-      <c r="N69" s="43" t="inlineStr"/>
+      <c r="J69" s="32" t="n"/>
+      <c r="K69" s="32" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="n"/>
@@ -4203,40 +3705,20 @@
       <c r="Z69" s="1" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B70" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C70" s="43" t="inlineStr">
-        <is>
-          <t>17/69</t>
-        </is>
-      </c>
-      <c r="D70" s="43" t="n">
-        <v>129.1</v>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
-      <c r="J70" s="44" t="inlineStr">
-        <is>
-          <t>אשכול כנרת</t>
-        </is>
-      </c>
-      <c r="K70" s="44" t="n">
-        <v>37538063</v>
-      </c>
-      <c r="L70" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M70" s="43" t="inlineStr"/>
-      <c r="N70" s="43" t="inlineStr"/>
+      <c r="J70" s="32" t="n"/>
+      <c r="K70" s="32" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="n"/>
@@ -4251,40 +3733,20 @@
       <c r="Z70" s="1" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B71" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C71" s="43" t="inlineStr">
-        <is>
-          <t>17/70</t>
-        </is>
-      </c>
-      <c r="D71" s="43" t="n">
-        <v>119.4</v>
-      </c>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
-      <c r="J71" s="44" t="inlineStr">
-        <is>
-          <t>ארד ליאה</t>
-        </is>
-      </c>
-      <c r="K71" s="44" t="n">
-        <v>56133440</v>
-      </c>
-      <c r="L71" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M71" s="43" t="inlineStr"/>
-      <c r="N71" s="43" t="inlineStr"/>
+      <c r="J71" s="32" t="n"/>
+      <c r="K71" s="32" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="n"/>
@@ -4299,42 +3761,20 @@
       <c r="Z71" s="1" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B72" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C72" s="43" t="inlineStr">
-        <is>
-          <t>17/71</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="n">
-        <v>136.25</v>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
-      <c r="J72" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K72" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L72" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M72" s="43" t="inlineStr"/>
-      <c r="N72" s="43" t="inlineStr"/>
+      <c r="J72" s="32" t="n"/>
+      <c r="K72" s="32" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
       <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="n"/>
@@ -4349,42 +3789,20 @@
       <c r="Z72" s="1" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B73" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C73" s="43" t="inlineStr">
-        <is>
-          <t>17/72</t>
-        </is>
-      </c>
-      <c r="D73" s="43" t="n">
-        <v>107.7</v>
-      </c>
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
-      <c r="J73" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K73" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L73" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M73" s="43" t="inlineStr"/>
-      <c r="N73" s="43" t="inlineStr"/>
+      <c r="J73" s="32" t="n"/>
+      <c r="K73" s="32" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="n"/>
@@ -4399,51 +3817,21 @@
       <c r="Z73" s="1" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B74" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C74" s="43" t="inlineStr">
-        <is>
-          <t>17/73</t>
-        </is>
-      </c>
-      <c r="D74" s="43" t="n">
-        <v>129.1</v>
-      </c>
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
-      <c r="J74" s="44" t="inlineStr">
-        <is>
-          <t>לויט קרייג מרק</t>
-        </is>
-      </c>
-      <c r="K74" s="44" t="n">
-        <v>323501007</v>
-      </c>
-      <c r="L74" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M74" s="43" t="inlineStr">
-        <is>
-          <t>מתתיה לויט רחלי</t>
-        </is>
-      </c>
-      <c r="N74" s="43" t="n">
-        <v>305263337</v>
-      </c>
-      <c r="O74" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J74" s="32" t="n"/>
+      <c r="K74" s="32" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="n"/>
       <c r="Q74" s="2" t="n"/>
       <c r="R74" s="2" t="n"/>
@@ -4457,42 +3845,20 @@
       <c r="Z74" s="1" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B75" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C75" s="43" t="inlineStr">
-        <is>
-          <t>17/74</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
-      <c r="J75" s="44" t="inlineStr">
-        <is>
-          <t>לבנת גזית יואב</t>
-        </is>
-      </c>
-      <c r="K75" s="44" t="n">
-        <v>328463872</v>
-      </c>
-      <c r="L75" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M75" s="43" t="inlineStr"/>
-      <c r="N75" s="43" t="inlineStr"/>
+      <c r="J75" s="32" t="n"/>
+      <c r="K75" s="32" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="n"/>
       <c r="Q75" s="2" t="n"/>
@@ -4507,42 +3873,20 @@
       <c r="Z75" s="1" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B76" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C76" s="43" t="inlineStr">
-        <is>
-          <t>17/75</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="n">
-        <v>136.25</v>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
-      <c r="J76" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K76" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L76" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M76" s="43" t="inlineStr"/>
-      <c r="N76" s="43" t="inlineStr"/>
+      <c r="J76" s="32" t="n"/>
+      <c r="K76" s="32" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="n"/>
       <c r="Q76" s="2" t="n"/>
@@ -4557,42 +3901,20 @@
       <c r="Z76" s="1" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B77" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C77" s="43" t="inlineStr">
-        <is>
-          <t>17/76</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
-      <c r="J77" s="44" t="inlineStr">
-        <is>
-          <t>בר יונה מילי</t>
-        </is>
-      </c>
-      <c r="K77" s="44" t="n">
-        <v>28583508</v>
-      </c>
-      <c r="L77" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M77" s="43" t="inlineStr"/>
-      <c r="N77" s="43" t="inlineStr"/>
+      <c r="J77" s="32" t="n"/>
+      <c r="K77" s="32" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="n"/>
+      <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
@@ -4607,42 +3929,20 @@
       <c r="Z77" s="1" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B78" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C78" s="43" t="inlineStr">
-        <is>
-          <t>17/77</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="n">
-        <v>171.8</v>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
-      <c r="J78" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K78" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L78" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M78" s="43" t="inlineStr"/>
-      <c r="N78" s="43" t="inlineStr"/>
+      <c r="J78" s="32" t="n"/>
+      <c r="K78" s="32" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
@@ -4657,42 +3957,20 @@
       <c r="Z78" s="1" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B79" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C79" s="43" t="inlineStr">
-        <is>
-          <t>17/78</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="n">
-        <v>132.45</v>
-      </c>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
-      <c r="J79" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K79" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L79" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M79" s="43" t="inlineStr"/>
-      <c r="N79" s="43" t="inlineStr"/>
+      <c r="J79" s="32" t="n"/>
+      <c r="K79" s="32" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
       <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="n"/>
@@ -4707,51 +3985,21 @@
       <c r="Z79" s="1" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B80" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C80" s="43" t="inlineStr">
-        <is>
-          <t>17/79</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="n">
-        <v>153.1</v>
-      </c>
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
-      <c r="J80" s="44" t="inlineStr">
-        <is>
-          <t>ליסקובסקי אלחנדרו חוסה</t>
-        </is>
-      </c>
-      <c r="K80" s="44" t="n">
-        <v>312711161</v>
-      </c>
-      <c r="L80" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M80" s="43" t="inlineStr">
-        <is>
-          <t>ליסקובסקי מריסה נעמי</t>
-        </is>
-      </c>
-      <c r="N80" s="43" t="n">
-        <v>312711211</v>
-      </c>
-      <c r="O80" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J80" s="32" t="n"/>
+      <c r="K80" s="32" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
       <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="n"/>
       <c r="R80" s="2" t="n"/>
@@ -4765,40 +4013,20 @@
       <c r="Z80" s="1" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B81" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C81" s="43" t="inlineStr">
-        <is>
-          <t>17/80</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="n">
-        <v>138.45</v>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
-      <c r="J81" s="44" t="inlineStr">
-        <is>
-          <t>חרזי שלו</t>
-        </is>
-      </c>
-      <c r="K81" s="44" t="n">
-        <v>25356502</v>
-      </c>
-      <c r="L81" s="43" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="M81" s="43" t="inlineStr"/>
-      <c r="N81" s="43" t="inlineStr"/>
+      <c r="J81" s="32" t="n"/>
+      <c r="K81" s="32" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n"/>
+      <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="n"/>
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
@@ -4813,42 +4041,20 @@
       <c r="Z81" s="1" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B82" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C82" s="43" t="inlineStr">
-        <is>
-          <t>17/81</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="n">
-        <v>134.8</v>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
-      <c r="J82" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K82" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L82" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M82" s="43" t="inlineStr"/>
-      <c r="N82" s="43" t="inlineStr"/>
+      <c r="J82" s="32" t="n"/>
+      <c r="K82" s="32" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="n"/>
       <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
@@ -4863,42 +4069,20 @@
       <c r="Z82" s="1" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B83" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C83" s="43" t="inlineStr">
-        <is>
-          <t>17/82</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="n">
-        <v>155.8</v>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="n"/>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
-      <c r="J83" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K83" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L83" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M83" s="43" t="inlineStr"/>
-      <c r="N83" s="43" t="inlineStr"/>
+      <c r="J83" s="32" t="n"/>
+      <c r="K83" s="32" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
       <c r="O83" s="2" t="n"/>
       <c r="P83" s="2" t="n"/>
       <c r="Q83" s="2" t="n"/>
@@ -4913,42 +4097,20 @@
       <c r="Z83" s="1" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B84" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C84" s="43" t="inlineStr">
-        <is>
-          <t>17/83</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="n">
-        <v>149.25</v>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
-      <c r="J84" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K84" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L84" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M84" s="43" t="inlineStr"/>
-      <c r="N84" s="43" t="inlineStr"/>
+      <c r="J84" s="32" t="n"/>
+      <c r="K84" s="32" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
       <c r="O84" s="2" t="n"/>
       <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="n"/>
@@ -4963,51 +4125,21 @@
       <c r="Z84" s="1" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B85" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C85" s="43" t="inlineStr">
-        <is>
-          <t>17/84</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
-      <c r="J85" s="44" t="inlineStr">
-        <is>
-          <t>לביא ארן</t>
-        </is>
-      </c>
-      <c r="K85" s="44" t="n">
-        <v>13677158</v>
-      </c>
-      <c r="L85" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M85" s="43" t="inlineStr">
-        <is>
-          <t>יוגב לביא נעמה שפי</t>
-        </is>
-      </c>
-      <c r="N85" s="43" t="n">
-        <v>34093260</v>
-      </c>
-      <c r="O85" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J85" s="32" t="n"/>
+      <c r="K85" s="32" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n"/>
+      <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="n"/>
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="n"/>
       <c r="R85" s="2" t="n"/>
@@ -5021,51 +4153,21 @@
       <c r="Z85" s="1" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B86" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C86" s="43" t="inlineStr">
-        <is>
-          <t>17/85</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="n">
-        <v>128.15</v>
-      </c>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
-      <c r="J86" s="44" t="inlineStr">
-        <is>
-          <t>זהבי יוסף</t>
-        </is>
-      </c>
-      <c r="K86" s="44" t="n">
-        <v>54563135</v>
-      </c>
-      <c r="L86" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M86" s="43" t="inlineStr">
-        <is>
-          <t>זהבי יוסף</t>
-        </is>
-      </c>
-      <c r="N86" s="43" t="n">
-        <v>54563135</v>
-      </c>
-      <c r="O86" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J86" s="32" t="n"/>
+      <c r="K86" s="32" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
       <c r="R86" s="2" t="n"/>
@@ -5079,51 +4181,21 @@
       <c r="Z86" s="1" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B87" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C87" s="43" t="inlineStr">
-        <is>
-          <t>17/86</t>
-        </is>
-      </c>
-      <c r="D87" s="43" t="n">
-        <v>149.65</v>
-      </c>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
-      <c r="J87" s="44" t="inlineStr">
-        <is>
-          <t>הימליך ניר</t>
-        </is>
-      </c>
-      <c r="K87" s="44" t="n">
-        <v>21601976</v>
-      </c>
-      <c r="L87" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M87" s="43" t="inlineStr">
-        <is>
-          <t>היימליך מיכל</t>
-        </is>
-      </c>
-      <c r="N87" s="43" t="n">
-        <v>310998026</v>
-      </c>
-      <c r="O87" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J87" s="32" t="n"/>
+      <c r="K87" s="32" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n"/>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="n"/>
@@ -5137,40 +4209,20 @@
       <c r="Z87" s="1" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B88" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C88" s="43" t="inlineStr">
-        <is>
-          <t>17/87</t>
-        </is>
-      </c>
-      <c r="D88" s="43" t="n">
-        <v>90.95</v>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
-      <c r="J88" s="44" t="inlineStr">
-        <is>
-          <t>חסון יפעת</t>
-        </is>
-      </c>
-      <c r="K88" s="44" t="n">
-        <v>34285619</v>
-      </c>
-      <c r="L88" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M88" s="43" t="inlineStr"/>
-      <c r="N88" s="43" t="inlineStr"/>
+      <c r="J88" s="32" t="n"/>
+      <c r="K88" s="32" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
       <c r="O88" s="2" t="n"/>
       <c r="P88" s="2" t="n"/>
       <c r="Q88" s="2" t="n"/>
@@ -5185,51 +4237,21 @@
       <c r="Z88" s="1" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B89" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C89" s="43" t="inlineStr">
-        <is>
-          <t>17/88</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="n">
-        <v>141.75</v>
-      </c>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
-      <c r="J89" s="44" t="inlineStr">
-        <is>
-          <t>עמרן לאה</t>
-        </is>
-      </c>
-      <c r="K89" s="44" t="n">
-        <v>319141248</v>
-      </c>
-      <c r="L89" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M89" s="43" t="inlineStr">
-        <is>
-          <t>עמרן זיו</t>
-        </is>
-      </c>
-      <c r="N89" s="43" t="n">
-        <v>313384323</v>
-      </c>
-      <c r="O89" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J89" s="32" t="n"/>
+      <c r="K89" s="32" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
       <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="n"/>
@@ -5243,51 +4265,21 @@
       <c r="Z89" s="1" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B90" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>17/89</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
-      <c r="J90" s="44" t="inlineStr">
-        <is>
-          <t>אופיר נועה</t>
-        </is>
-      </c>
-      <c r="K90" s="44" t="n">
-        <v>305624710</v>
-      </c>
-      <c r="L90" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M90" s="43" t="inlineStr">
-        <is>
-          <t>אופיר גרשון</t>
-        </is>
-      </c>
-      <c r="N90" s="43" t="n">
-        <v>303955827</v>
-      </c>
-      <c r="O90" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J90" s="32" t="n"/>
+      <c r="K90" s="32" t="n"/>
+      <c r="L90" s="2" t="n"/>
+      <c r="M90" s="2" t="n"/>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
       <c r="P90" s="2" t="n"/>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="n"/>
@@ -5301,40 +4293,20 @@
       <c r="Z90" s="1" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B91" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C91" s="43" t="inlineStr">
-        <is>
-          <t>17/90</t>
-        </is>
-      </c>
-      <c r="D91" s="43" t="n">
-        <v>128.15</v>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
-      <c r="J91" s="44" t="inlineStr">
-        <is>
-          <t>טקו אלה</t>
-        </is>
-      </c>
-      <c r="K91" s="44" t="n">
-        <v>27940014</v>
-      </c>
-      <c r="L91" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M91" s="43" t="inlineStr"/>
-      <c r="N91" s="43" t="inlineStr"/>
+      <c r="J91" s="32" t="n"/>
+      <c r="K91" s="32" t="n"/>
+      <c r="L91" s="2" t="n"/>
+      <c r="M91" s="2" t="n"/>
+      <c r="N91" s="2" t="n"/>
       <c r="O91" s="2" t="n"/>
       <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
@@ -5349,42 +4321,20 @@
       <c r="Z91" s="1" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B92" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C92" s="43" t="inlineStr">
-        <is>
-          <t>17/91</t>
-        </is>
-      </c>
-      <c r="D92" s="43" t="n">
-        <v>149.65</v>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
-      <c r="J92" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K92" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L92" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M92" s="43" t="inlineStr"/>
-      <c r="N92" s="43" t="inlineStr"/>
+      <c r="J92" s="32" t="n"/>
+      <c r="K92" s="32" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
@@ -5399,51 +4349,21 @@
       <c r="Z92" s="1" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B93" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C93" s="43" t="inlineStr">
-        <is>
-          <t>17/92</t>
-        </is>
-      </c>
-      <c r="D93" s="43" t="n">
-        <v>90.95</v>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="n"/>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
-      <c r="J93" s="44" t="inlineStr">
-        <is>
-          <t>ינקו כהן אורטל</t>
-        </is>
-      </c>
-      <c r="K93" s="44" t="n">
-        <v>36920700</v>
-      </c>
-      <c r="L93" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M93" s="43" t="inlineStr">
-        <is>
-          <t>כהן רועי</t>
-        </is>
-      </c>
-      <c r="N93" s="43" t="n">
-        <v>39274220</v>
-      </c>
-      <c r="O93" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J93" s="32" t="n"/>
+      <c r="K93" s="32" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="2" t="n"/>
@@ -5457,51 +4377,21 @@
       <c r="Z93" s="1" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B94" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C94" s="43" t="inlineStr">
-        <is>
-          <t>17/93</t>
-        </is>
-      </c>
-      <c r="D94" s="43" t="n">
-        <v>141.75</v>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
-      <c r="J94" s="44" t="inlineStr">
-        <is>
-          <t>עיני אדוה</t>
-        </is>
-      </c>
-      <c r="K94" s="44" t="n">
-        <v>36908382</v>
-      </c>
-      <c r="L94" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M94" s="43" t="inlineStr">
-        <is>
-          <t>ששון עדן</t>
-        </is>
-      </c>
-      <c r="N94" s="43" t="n">
-        <v>17874868</v>
-      </c>
-      <c r="O94" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J94" s="32" t="n"/>
+      <c r="K94" s="32" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="n"/>
@@ -5515,40 +4405,20 @@
       <c r="Z94" s="1" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B95" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C95" s="43" t="inlineStr">
-        <is>
-          <t>17/94</t>
-        </is>
-      </c>
-      <c r="D95" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
-      <c r="J95" s="44" t="inlineStr">
-        <is>
-          <t>יעיש לידר</t>
-        </is>
-      </c>
-      <c r="K95" s="44" t="n">
-        <v>305210759</v>
-      </c>
-      <c r="L95" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M95" s="43" t="inlineStr"/>
-      <c r="N95" s="43" t="inlineStr"/>
+      <c r="J95" s="32" t="n"/>
+      <c r="K95" s="32" t="n"/>
+      <c r="L95" s="2" t="n"/>
+      <c r="M95" s="2" t="n"/>
+      <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="n"/>
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="n"/>
@@ -5563,45 +4433,21 @@
       <c r="Z95" s="1" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B96" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C96" s="43" t="inlineStr">
-        <is>
-          <t>17/95</t>
-        </is>
-      </c>
-      <c r="D96" s="43" t="n">
-        <v>128.15</v>
-      </c>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n"/>
       <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
-      <c r="J96" s="44" t="inlineStr">
-        <is>
-          <t>דיין דבורה</t>
-        </is>
-      </c>
-      <c r="K96" s="44" t="n">
-        <v>56464829</v>
-      </c>
-      <c r="L96" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M96" s="43" t="inlineStr"/>
-      <c r="N96" s="43" t="inlineStr"/>
-      <c r="O96" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J96" s="32" t="n"/>
+      <c r="K96" s="32" t="n"/>
+      <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="n"/>
       <c r="R96" s="2" t="n"/>
@@ -5615,42 +4461,20 @@
       <c r="Z96" s="1" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B97" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C97" s="43" t="inlineStr">
-        <is>
-          <t>17/96</t>
-        </is>
-      </c>
-      <c r="D97" s="43" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n"/>
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
-      <c r="J97" s="44" t="inlineStr">
-        <is>
-          <t>משולם רועי</t>
-        </is>
-      </c>
-      <c r="K97" s="44" t="n">
-        <v>39672886</v>
-      </c>
-      <c r="L97" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M97" s="43" t="inlineStr"/>
-      <c r="N97" s="43" t="inlineStr"/>
+      <c r="J97" s="32" t="n"/>
+      <c r="K97" s="32" t="n"/>
+      <c r="L97" s="2" t="n"/>
+      <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
       <c r="O97" s="2" t="n"/>
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
@@ -5665,40 +4489,20 @@
       <c r="Z97" s="1" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B98" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C98" s="43" t="inlineStr">
-        <is>
-          <t>17/97</t>
-        </is>
-      </c>
-      <c r="D98" s="43" t="n">
-        <v>90.95</v>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n"/>
       <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
-      <c r="J98" s="44" t="inlineStr">
-        <is>
-          <t>הרשקוביץ יוסף</t>
-        </is>
-      </c>
-      <c r="K98" s="44" t="n">
-        <v>67129759</v>
-      </c>
-      <c r="L98" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M98" s="43" t="inlineStr"/>
-      <c r="N98" s="43" t="inlineStr"/>
+      <c r="J98" s="32" t="n"/>
+      <c r="K98" s="32" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
       <c r="O98" s="2" t="n"/>
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="n"/>
@@ -5713,53 +4517,21 @@
       <c r="Z98" s="1" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B99" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C99" s="43" t="inlineStr">
-        <is>
-          <t>17/98</t>
-        </is>
-      </c>
-      <c r="D99" s="43" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
-      <c r="J99" s="44" t="inlineStr">
-        <is>
-          <t>מור נעמה</t>
-        </is>
-      </c>
-      <c r="K99" s="44" t="n">
-        <v>200422335</v>
-      </c>
-      <c r="L99" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M99" s="43" t="inlineStr">
-        <is>
-          <t>בקלצוק יואב</t>
-        </is>
-      </c>
-      <c r="N99" s="43" t="n">
-        <v>300883972</v>
-      </c>
-      <c r="O99" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J99" s="32" t="n"/>
+      <c r="K99" s="32" t="n"/>
+      <c r="L99" s="2" t="n"/>
+      <c r="M99" s="2" t="n"/>
+      <c r="N99" s="2" t="n"/>
+      <c r="O99" s="2" t="n"/>
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="n"/>
@@ -5773,40 +4545,20 @@
       <c r="Z99" s="1" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B100" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C100" s="43" t="inlineStr">
-        <is>
-          <t>17/99</t>
-        </is>
-      </c>
-      <c r="D100" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
-      <c r="J100" s="44" t="inlineStr">
-        <is>
-          <t>כהן גינזברג אורנה</t>
-        </is>
-      </c>
-      <c r="K100" s="44" t="n">
-        <v>53626669</v>
-      </c>
-      <c r="L100" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M100" s="43" t="inlineStr"/>
-      <c r="N100" s="43" t="inlineStr"/>
+      <c r="J100" s="32" t="n"/>
+      <c r="K100" s="32" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="n"/>
       <c r="P100" s="2" t="n"/>
       <c r="Q100" s="2" t="n"/>
@@ -5821,40 +4573,20 @@
       <c r="Z100" s="1" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B101" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C101" s="43" t="inlineStr">
-        <is>
-          <t>17/100</t>
-        </is>
-      </c>
-      <c r="D101" s="43" t="n">
-        <v>128.15</v>
-      </c>
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n"/>
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
-      <c r="J101" s="44" t="inlineStr">
-        <is>
-          <t>ויימן לוין עדי בלה</t>
-        </is>
-      </c>
-      <c r="K101" s="44" t="n">
-        <v>28662567</v>
-      </c>
-      <c r="L101" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M101" s="43" t="inlineStr"/>
-      <c r="N101" s="43" t="inlineStr"/>
+      <c r="J101" s="32" t="n"/>
+      <c r="K101" s="32" t="n"/>
+      <c r="L101" s="2" t="n"/>
+      <c r="M101" s="2" t="n"/>
+      <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n"/>
       <c r="P101" s="2" t="n"/>
       <c r="Q101" s="2" t="n"/>
@@ -5869,51 +4601,21 @@
       <c r="Z101" s="1" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B102" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C102" s="43" t="inlineStr">
-        <is>
-          <t>17/101</t>
-        </is>
-      </c>
-      <c r="D102" s="43" t="n">
-        <v>149.65</v>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n"/>
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
-      <c r="J102" s="44" t="inlineStr">
-        <is>
-          <t>שאלתיאל רעות</t>
-        </is>
-      </c>
-      <c r="K102" s="44" t="n">
-        <v>312505332</v>
-      </c>
-      <c r="L102" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M102" s="43" t="inlineStr">
-        <is>
-          <t>שאלתיאל שלום</t>
-        </is>
-      </c>
-      <c r="N102" s="43" t="n">
-        <v>305327603</v>
-      </c>
-      <c r="O102" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J102" s="32" t="n"/>
+      <c r="K102" s="32" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
       <c r="P102" s="2" t="n"/>
       <c r="Q102" s="2" t="n"/>
       <c r="R102" s="2" t="n"/>
@@ -5927,45 +4629,21 @@
       <c r="Z102" s="1" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B103" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C103" s="43" t="inlineStr">
-        <is>
-          <t>17/102</t>
-        </is>
-      </c>
-      <c r="D103" s="43" t="n">
-        <v>90.95</v>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="n"/>
       <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
-      <c r="J103" s="44" t="inlineStr">
-        <is>
-          <t>בן ישי שמעון</t>
-        </is>
-      </c>
-      <c r="K103" s="44" t="n">
-        <v>54713755</v>
-      </c>
-      <c r="L103" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M103" s="43" t="inlineStr"/>
-      <c r="N103" s="43" t="inlineStr"/>
-      <c r="O103" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J103" s="32" t="n"/>
+      <c r="K103" s="32" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="n"/>
@@ -5979,40 +4657,20 @@
       <c r="Z103" s="1" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B104" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C104" s="43" t="inlineStr">
-        <is>
-          <t>17/103</t>
-        </is>
-      </c>
-      <c r="D104" s="43" t="n">
-        <v>141.75</v>
-      </c>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="n"/>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
-      <c r="J104" s="44" t="inlineStr">
-        <is>
-          <t>מני רוחמה</t>
-        </is>
-      </c>
-      <c r="K104" s="44" t="n">
-        <v>58651076</v>
-      </c>
-      <c r="L104" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M104" s="43" t="inlineStr"/>
-      <c r="N104" s="43" t="inlineStr"/>
+      <c r="J104" s="32" t="n"/>
+      <c r="K104" s="32" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
       <c r="O104" s="2" t="n"/>
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="n"/>
@@ -6027,45 +4685,21 @@
       <c r="Z104" s="1" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B105" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C105" s="43" t="inlineStr">
-        <is>
-          <t>17/104</t>
-        </is>
-      </c>
-      <c r="D105" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="n"/>
       <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
-      <c r="J105" s="44" t="inlineStr">
-        <is>
-          <t>רופא כפיר</t>
-        </is>
-      </c>
-      <c r="K105" s="44" t="n">
-        <v>25358664</v>
-      </c>
-      <c r="L105" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M105" s="43" t="inlineStr"/>
-      <c r="N105" s="43" t="inlineStr"/>
-      <c r="O105" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J105" s="32" t="n"/>
+      <c r="K105" s="32" t="n"/>
+      <c r="L105" s="2" t="n"/>
+      <c r="M105" s="2" t="n"/>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
       <c r="P105" s="2" t="n"/>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
@@ -6079,46 +4713,20 @@
       <c r="Z105" s="1" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B106" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C106" s="43" t="inlineStr">
-        <is>
-          <t>17/105</t>
-        </is>
-      </c>
-      <c r="D106" s="43" t="n">
-        <v>128.15</v>
-      </c>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n"/>
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
-      <c r="J106" s="44" t="inlineStr">
-        <is>
-          <t>דרך רמאל שלום</t>
-        </is>
-      </c>
-      <c r="K106" s="44" t="n">
-        <v>22933535</v>
-      </c>
-      <c r="L106" s="43" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="M106" s="43" t="inlineStr">
-        <is>
-          <t>עקירב שמרית</t>
-        </is>
-      </c>
-      <c r="N106" s="43" t="n">
-        <v>32559791</v>
-      </c>
+      <c r="J106" s="32" t="n"/>
+      <c r="K106" s="32" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
       <c r="O106" s="2" t="n"/>
       <c r="P106" s="2" t="n"/>
       <c r="Q106" s="2" t="n"/>
@@ -6133,40 +4741,20 @@
       <c r="Z106" s="1" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B107" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C107" s="43" t="inlineStr">
-        <is>
-          <t>17/106</t>
-        </is>
-      </c>
-      <c r="D107" s="43" t="n">
-        <v>134.55</v>
-      </c>
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
-      <c r="J107" s="44" t="inlineStr">
-        <is>
-          <t>בן דוד קנדיס</t>
-        </is>
-      </c>
-      <c r="K107" s="44" t="n">
-        <v>33406372</v>
-      </c>
-      <c r="L107" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M107" s="43" t="inlineStr"/>
-      <c r="N107" s="43" t="inlineStr"/>
+      <c r="J107" s="32" t="n"/>
+      <c r="K107" s="32" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
       <c r="O107" s="2" t="n"/>
       <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="n"/>
@@ -6181,40 +4769,20 @@
       <c r="Z107" s="1" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B108" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C108" s="43" t="inlineStr">
-        <is>
-          <t>17/107</t>
-        </is>
-      </c>
-      <c r="D108" s="43" t="n">
-        <v>90.95</v>
-      </c>
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
-      <c r="J108" s="44" t="inlineStr">
-        <is>
-          <t>מעוז אביבית</t>
-        </is>
-      </c>
-      <c r="K108" s="44" t="n">
-        <v>34856104</v>
-      </c>
-      <c r="L108" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M108" s="45" t="inlineStr"/>
-      <c r="N108" s="43" t="inlineStr"/>
+      <c r="J108" s="32" t="n"/>
+      <c r="K108" s="32" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="4" t="n"/>
+      <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="n"/>
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="n"/>
@@ -6229,40 +4797,20 @@
       <c r="Z108" s="1" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B109" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C109" s="43" t="inlineStr">
-        <is>
-          <t>17/108</t>
-        </is>
-      </c>
-      <c r="D109" s="43" t="n">
-        <v>141.75</v>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n"/>
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
-      <c r="J109" s="44" t="inlineStr">
-        <is>
-          <t>קפר נעמה</t>
-        </is>
-      </c>
-      <c r="K109" s="44" t="n">
-        <v>318592482</v>
-      </c>
-      <c r="L109" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M109" s="43" t="inlineStr"/>
-      <c r="N109" s="43" t="inlineStr"/>
+      <c r="J109" s="32" t="n"/>
+      <c r="K109" s="32" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="n"/>
       <c r="O109" s="2" t="n"/>
       <c r="P109" s="2" t="n"/>
       <c r="Q109" s="2" t="n"/>
@@ -6277,51 +4825,21 @@
       <c r="Z109" s="1" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B110" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C110" s="43" t="inlineStr">
-        <is>
-          <t>17/109</t>
-        </is>
-      </c>
-      <c r="D110" s="43" t="n">
-        <v>119.45</v>
-      </c>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
-      <c r="J110" s="44" t="inlineStr">
-        <is>
-          <t>חירק אודיה</t>
-        </is>
-      </c>
-      <c r="K110" s="44" t="n">
-        <v>204058598</v>
-      </c>
-      <c r="L110" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M110" s="43" t="inlineStr">
-        <is>
-          <t>חירק נתנאל</t>
-        </is>
-      </c>
-      <c r="N110" s="43" t="n">
-        <v>302439815</v>
-      </c>
-      <c r="O110" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J110" s="32" t="n"/>
+      <c r="K110" s="32" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="n"/>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
@@ -6335,40 +4853,20 @@
       <c r="Z110" s="1" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B111" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C111" s="43" t="inlineStr">
-        <is>
-          <t>17/110</t>
-        </is>
-      </c>
-      <c r="D111" s="43" t="n">
-        <v>149.05</v>
-      </c>
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n"/>
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
-      <c r="J111" s="44" t="inlineStr">
-        <is>
-          <t>כהן ניצה</t>
-        </is>
-      </c>
-      <c r="K111" s="44" t="n">
-        <v>56067556</v>
-      </c>
-      <c r="L111" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M111" s="43" t="inlineStr"/>
-      <c r="N111" s="43" t="inlineStr"/>
+      <c r="J111" s="32" t="n"/>
+      <c r="K111" s="32" t="n"/>
+      <c r="L111" s="2" t="n"/>
+      <c r="M111" s="2" t="n"/>
+      <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="n"/>
@@ -6383,40 +4881,20 @@
       <c r="Z111" s="1" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B112" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C112" s="43" t="inlineStr">
-        <is>
-          <t>17/111</t>
-        </is>
-      </c>
-      <c r="D112" s="43" t="n">
-        <v>126.75</v>
-      </c>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
-      <c r="J112" s="44" t="inlineStr">
-        <is>
-          <t>מקמל מוניק</t>
-        </is>
-      </c>
-      <c r="K112" s="44" t="n">
-        <v>69762250</v>
-      </c>
-      <c r="L112" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M112" s="43" t="inlineStr"/>
-      <c r="N112" s="43" t="inlineStr"/>
+      <c r="J112" s="32" t="n"/>
+      <c r="K112" s="32" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="n"/>
@@ -6431,40 +4909,20 @@
       <c r="Z112" s="1" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B113" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C113" s="43" t="inlineStr">
-        <is>
-          <t>17/112</t>
-        </is>
-      </c>
-      <c r="D113" s="43" t="n">
-        <v>141.95</v>
-      </c>
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="n"/>
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
-      <c r="J113" s="44" t="inlineStr">
-        <is>
-          <t>אמר מיכל</t>
-        </is>
-      </c>
-      <c r="K113" s="46" t="n">
-        <v>201469731</v>
-      </c>
-      <c r="L113" s="43" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="M113" s="43" t="inlineStr"/>
-      <c r="N113" s="43" t="inlineStr"/>
+      <c r="J113" s="32" t="n"/>
+      <c r="K113" s="33" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="n"/>
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="n"/>
@@ -6479,51 +4937,21 @@
       <c r="Z113" s="1" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B114" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C114" s="43" t="inlineStr">
-        <is>
-          <t>17/113</t>
-        </is>
-      </c>
-      <c r="D114" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="n"/>
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
-      <c r="J114" s="44" t="inlineStr">
-        <is>
-          <t>אברהם שבתאי שי</t>
-        </is>
-      </c>
-      <c r="K114" s="44" t="n">
-        <v>66648569</v>
-      </c>
-      <c r="L114" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M114" s="43" t="inlineStr">
-        <is>
-          <t>לבל אברהם סיון</t>
-        </is>
-      </c>
-      <c r="N114" s="43" t="n">
-        <v>66367343</v>
-      </c>
-      <c r="O114" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J114" s="32" t="n"/>
+      <c r="K114" s="32" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="n"/>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
@@ -6537,40 +4965,20 @@
       <c r="Z114" s="1" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B115" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C115" s="43" t="inlineStr">
-        <is>
-          <t>17/114</t>
-        </is>
-      </c>
-      <c r="D115" s="43" t="n">
-        <v>148.75</v>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
-      <c r="J115" s="44" t="inlineStr">
-        <is>
-          <t>סופר חזן אודליה</t>
-        </is>
-      </c>
-      <c r="K115" s="44" t="n">
-        <v>34415117</v>
-      </c>
-      <c r="L115" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M115" s="43" t="inlineStr"/>
-      <c r="N115" s="43" t="inlineStr"/>
+      <c r="J115" s="32" t="n"/>
+      <c r="K115" s="32" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" s="2" t="n"/>
+      <c r="N115" s="2" t="n"/>
       <c r="O115" s="2" t="n"/>
       <c r="P115" s="2" t="n"/>
       <c r="Q115" s="2" t="n"/>
@@ -6585,40 +4993,20 @@
       <c r="Z115" s="1" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B116" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C116" s="43" t="inlineStr">
-        <is>
-          <t>17/115</t>
-        </is>
-      </c>
-      <c r="D116" s="43" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
-      <c r="J116" s="44" t="inlineStr">
-        <is>
-          <t>קריבנקו ניולו סטניסלב</t>
-        </is>
-      </c>
-      <c r="K116" s="44" t="n">
-        <v>321865966</v>
-      </c>
-      <c r="L116" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M116" s="43" t="inlineStr"/>
-      <c r="N116" s="43" t="inlineStr"/>
+      <c r="J116" s="32" t="n"/>
+      <c r="K116" s="32" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="2" t="n"/>
+      <c r="N116" s="2" t="n"/>
       <c r="O116" s="2" t="n"/>
       <c r="P116" s="2" t="n"/>
       <c r="Q116" s="2" t="n"/>
@@ -6633,45 +5021,21 @@
       <c r="Z116" s="1" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B117" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C117" s="43" t="inlineStr">
-        <is>
-          <t>17/116</t>
-        </is>
-      </c>
-      <c r="D117" s="43" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
-      <c r="J117" s="44" t="inlineStr">
-        <is>
-          <t>אלבוחר קרן רבקה</t>
-        </is>
-      </c>
-      <c r="K117" s="44" t="n">
-        <v>209276104</v>
-      </c>
-      <c r="L117" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M117" s="43" t="inlineStr"/>
-      <c r="N117" s="43" t="inlineStr"/>
-      <c r="O117" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J117" s="32" t="n"/>
+      <c r="K117" s="32" t="n"/>
+      <c r="L117" s="2" t="n"/>
+      <c r="M117" s="2" t="n"/>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
       <c r="P117" s="5" t="n"/>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="n"/>
@@ -6685,40 +5049,20 @@
       <c r="Z117" s="1" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B118" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C118" s="43" t="inlineStr">
-        <is>
-          <t>17/117</t>
-        </is>
-      </c>
-      <c r="D118" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
       <c r="F118" s="2" t="n"/>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
-      <c r="J118" s="44" t="inlineStr">
-        <is>
-          <t>ריבל מיה</t>
-        </is>
-      </c>
-      <c r="K118" s="44" t="n">
-        <v>38329967</v>
-      </c>
-      <c r="L118" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M118" s="43" t="inlineStr"/>
-      <c r="N118" s="43" t="inlineStr"/>
+      <c r="J118" s="32" t="n"/>
+      <c r="K118" s="32" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="2" t="n"/>
+      <c r="N118" s="2" t="n"/>
       <c r="O118" s="2" t="n"/>
       <c r="P118" s="2" t="n"/>
       <c r="Q118" s="2" t="n"/>
@@ -6733,51 +5077,21 @@
       <c r="Z118" s="1" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B119" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C119" s="43" t="inlineStr">
-        <is>
-          <t>17/118</t>
-        </is>
-      </c>
-      <c r="D119" s="43" t="n">
-        <v>148.75</v>
-      </c>
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" s="2" t="n"/>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
-      <c r="J119" s="44" t="inlineStr">
-        <is>
-          <t>נגרקר ג'וייס</t>
-        </is>
-      </c>
-      <c r="K119" s="44" t="n">
-        <v>16850877</v>
-      </c>
-      <c r="L119" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M119" s="43" t="inlineStr">
-        <is>
-          <t>נגרקר דניאל</t>
-        </is>
-      </c>
-      <c r="N119" s="43" t="n">
-        <v>27042506</v>
-      </c>
-      <c r="O119" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J119" s="32" t="n"/>
+      <c r="K119" s="32" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
       <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="n"/>
       <c r="R119" s="2" t="n"/>
@@ -6791,51 +5105,21 @@
       <c r="Z119" s="1" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B120" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C120" s="43" t="inlineStr">
-        <is>
-          <t>17/119</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
-      <c r="J120" s="44" t="inlineStr">
-        <is>
-          <t>מזור יהודה</t>
-        </is>
-      </c>
-      <c r="K120" s="44" t="n">
-        <v>200946382</v>
-      </c>
-      <c r="L120" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M120" s="43" t="inlineStr">
-        <is>
-          <t>מזור נופר</t>
-        </is>
-      </c>
-      <c r="N120" s="43" t="n">
-        <v>305745572</v>
-      </c>
-      <c r="O120" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J120" s="32" t="n"/>
+      <c r="K120" s="32" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
       <c r="P120" s="2" t="n"/>
       <c r="Q120" s="2" t="n"/>
       <c r="R120" s="2" t="n"/>
@@ -6849,45 +5133,21 @@
       <c r="Z120" s="1" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B121" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C121" s="43" t="inlineStr">
-        <is>
-          <t>17/120</t>
-        </is>
-      </c>
-      <c r="D121" s="43" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" s="2" t="n"/>
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
-      <c r="J121" s="44" t="inlineStr">
-        <is>
-          <t>מנדס יפעת</t>
-        </is>
-      </c>
-      <c r="K121" s="44" t="n">
-        <v>27931039</v>
-      </c>
-      <c r="L121" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M121" s="43" t="inlineStr"/>
-      <c r="N121" s="43" t="inlineStr"/>
-      <c r="O121" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J121" s="32" t="n"/>
+      <c r="K121" s="32" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
       <c r="P121" s="2" t="n"/>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
@@ -6901,51 +5161,21 @@
       <c r="Z121" s="1" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B122" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C122" s="43" t="inlineStr">
-        <is>
-          <t>17/121</t>
-        </is>
-      </c>
-      <c r="D122" s="43" t="n">
-        <v>119.15</v>
-      </c>
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
       <c r="F122" s="2" t="n"/>
       <c r="G122" s="2" t="n"/>
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
-      <c r="J122" s="44" t="inlineStr">
-        <is>
-          <t>חייט צבטאני קסניה</t>
-        </is>
-      </c>
-      <c r="K122" s="44" t="n">
-        <v>323547513</v>
-      </c>
-      <c r="L122" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M122" s="43" t="inlineStr">
-        <is>
-          <t>צבטאני שי</t>
-        </is>
-      </c>
-      <c r="N122" s="43" t="n">
-        <v>29983871</v>
-      </c>
-      <c r="O122" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J122" s="32" t="n"/>
+      <c r="K122" s="32" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
       <c r="P122" s="2" t="n"/>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="2" t="n"/>
@@ -6959,53 +5189,21 @@
       <c r="Z122" s="1" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B123" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C123" s="43" t="inlineStr">
-        <is>
-          <t>17/122</t>
-        </is>
-      </c>
-      <c r="D123" s="43" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
-      <c r="J123" s="44" t="inlineStr">
-        <is>
-          <t>סגל אדר סמדר</t>
-        </is>
-      </c>
-      <c r="K123" s="44" t="n">
-        <v>28630234</v>
-      </c>
-      <c r="L123" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M123" s="43" t="inlineStr">
-        <is>
-          <t>וולף ריצ'רד האג</t>
-        </is>
-      </c>
-      <c r="N123" s="43" t="n">
-        <v>310026620</v>
-      </c>
-      <c r="O123" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J123" s="32" t="n"/>
+      <c r="K123" s="32" t="n"/>
+      <c r="L123" s="2" t="n"/>
+      <c r="M123" s="2" t="n"/>
+      <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
       <c r="P123" s="2" t="n"/>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="n"/>
@@ -7019,40 +5217,20 @@
       <c r="Z123" s="1" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B124" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C124" s="43" t="inlineStr">
-        <is>
-          <t>17/123</t>
-        </is>
-      </c>
-      <c r="D124" s="43" t="n">
-        <v>131.6</v>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
-      <c r="J124" s="44" t="inlineStr">
-        <is>
-          <t>זבידה אביבית</t>
-        </is>
-      </c>
-      <c r="K124" s="44" t="n">
-        <v>32397556</v>
-      </c>
-      <c r="L124" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M124" s="43" t="inlineStr"/>
-      <c r="N124" s="43" t="inlineStr"/>
+      <c r="J124" s="32" t="n"/>
+      <c r="K124" s="32" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="n"/>
       <c r="Q124" s="2" t="n"/>
@@ -7067,45 +5245,21 @@
       <c r="Z124" s="1" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B125" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C125" s="43" t="inlineStr">
-        <is>
-          <t>17/124</t>
-        </is>
-      </c>
-      <c r="D125" s="43" t="n">
-        <v>141.6</v>
-      </c>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
-      <c r="J125" s="44" t="inlineStr">
-        <is>
-          <t>פסט עמר דורין</t>
-        </is>
-      </c>
-      <c r="K125" s="44" t="n">
-        <v>38117370</v>
-      </c>
-      <c r="L125" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M125" s="43" t="inlineStr"/>
-      <c r="N125" s="43" t="inlineStr"/>
-      <c r="O125" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J125" s="32" t="n"/>
+      <c r="K125" s="32" t="n"/>
+      <c r="L125" s="2" t="n"/>
+      <c r="M125" s="2" t="n"/>
+      <c r="N125" s="2" t="n"/>
+      <c r="O125" s="2" t="n"/>
       <c r="P125" s="2" t="n"/>
       <c r="Q125" s="2" t="n"/>
       <c r="R125" s="2" t="n"/>
@@ -7119,51 +5273,21 @@
       <c r="Z125" s="1" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B126" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C126" s="43" t="inlineStr">
-        <is>
-          <t>17/125</t>
-        </is>
-      </c>
-      <c r="D126" s="43" t="n">
-        <v>107.7</v>
-      </c>
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
-      <c r="J126" s="44" t="inlineStr">
-        <is>
-          <t>בן דוד בנימין</t>
-        </is>
-      </c>
-      <c r="K126" s="44" t="n">
-        <v>27918341</v>
-      </c>
-      <c r="L126" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M126" s="43" t="inlineStr">
-        <is>
-          <t>אשר אילנית</t>
-        </is>
-      </c>
-      <c r="N126" s="43" t="n">
-        <v>31923097</v>
-      </c>
-      <c r="O126" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J126" s="32" t="n"/>
+      <c r="K126" s="32" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
       <c r="P126" s="2" t="n"/>
       <c r="Q126" s="2" t="n"/>
       <c r="R126" s="2" t="n"/>
@@ -7177,42 +5301,20 @@
       <c r="Z126" s="1" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B127" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C127" s="43" t="inlineStr">
-        <is>
-          <t>17/126</t>
-        </is>
-      </c>
-      <c r="D127" s="43" t="n">
-        <v>136.25</v>
-      </c>
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
-      <c r="J127" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K127" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L127" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M127" s="43" t="inlineStr"/>
-      <c r="N127" s="43" t="inlineStr"/>
+      <c r="J127" s="32" t="n"/>
+      <c r="K127" s="32" t="n"/>
+      <c r="L127" s="2" t="n"/>
+      <c r="M127" s="2" t="n"/>
+      <c r="N127" s="2" t="n"/>
       <c r="O127" s="2" t="n"/>
       <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="n"/>
@@ -7227,51 +5329,21 @@
       <c r="Z127" s="1" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B128" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C128" s="43" t="inlineStr">
-        <is>
-          <t>17/127</t>
-        </is>
-      </c>
-      <c r="D128" s="43" t="n">
-        <v>119.4</v>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="n"/>
       <c r="F128" s="2" t="n"/>
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="n"/>
-      <c r="J128" s="44" t="inlineStr">
-        <is>
-          <t>בן לוי נורליאן ספיר</t>
-        </is>
-      </c>
-      <c r="K128" s="44" t="n">
-        <v>204009138</v>
-      </c>
-      <c r="L128" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M128" s="43" t="inlineStr">
-        <is>
-          <t>נורליאן איתי</t>
-        </is>
-      </c>
-      <c r="N128" s="43" t="n">
-        <v>200460863</v>
-      </c>
-      <c r="O128" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J128" s="32" t="n"/>
+      <c r="K128" s="32" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
       <c r="P128" s="2" t="n"/>
       <c r="Q128" s="2" t="n"/>
       <c r="R128" s="2" t="n"/>
@@ -7285,45 +5357,21 @@
       <c r="Z128" s="1" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B129" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C129" s="43" t="inlineStr">
-        <is>
-          <t>17/128</t>
-        </is>
-      </c>
-      <c r="D129" s="43" t="n">
-        <v>129.1</v>
-      </c>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" s="2" t="n"/>
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
-      <c r="J129" s="44" t="inlineStr">
-        <is>
-          <t>כהן עמית</t>
-        </is>
-      </c>
-      <c r="K129" s="44" t="n">
-        <v>35728286</v>
-      </c>
-      <c r="L129" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M129" s="43" t="inlineStr"/>
-      <c r="N129" s="43" t="inlineStr"/>
-      <c r="O129" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J129" s="32" t="n"/>
+      <c r="K129" s="32" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="2" t="n"/>
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
       <c r="P129" s="2" t="n"/>
       <c r="Q129" s="2" t="n"/>
       <c r="R129" s="2" t="n"/>
@@ -7337,45 +5385,21 @@
       <c r="Z129" s="1" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B130" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C130" s="43" t="inlineStr">
-        <is>
-          <t>17/129</t>
-        </is>
-      </c>
-      <c r="D130" s="43" t="n">
-        <v>164.6</v>
-      </c>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="n"/>
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
-      <c r="J130" s="44" t="inlineStr">
-        <is>
-          <t>גורבצ'וב דריה</t>
-        </is>
-      </c>
-      <c r="K130" s="44" t="n">
-        <v>317145977</v>
-      </c>
-      <c r="L130" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="M130" s="43" t="inlineStr"/>
-      <c r="N130" s="43" t="inlineStr"/>
-      <c r="O130" s="43" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
+      <c r="J130" s="32" t="n"/>
+      <c r="K130" s="32" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="n"/>
       <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="n"/>
@@ -7389,42 +5413,20 @@
       <c r="Z130" s="1" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="43" t="n">
-        <v>7284</v>
-      </c>
-      <c r="B131" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C131" s="43" t="inlineStr">
-        <is>
-          <t>17/130</t>
-        </is>
-      </c>
-      <c r="D131" s="43" t="n">
-        <v>171.8</v>
-      </c>
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
-      <c r="J131" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K131" s="44" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="L131" s="43" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="M131" s="43" t="inlineStr"/>
-      <c r="N131" s="43" t="inlineStr"/>
+      <c r="J131" s="32" t="n"/>
+      <c r="K131" s="32" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
       <c r="O131" s="2" t="n"/>
       <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="n"/>
